--- a/C/10. SOFTWARE DESIGN IN C.xlsx
+++ b/C/10. SOFTWARE DESIGN IN C.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mục lục" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="537">
   <si>
     <t>🏗️ SOFTWARE DESIGN IN C</t>
   </si>
@@ -492,9 +492,6 @@
     <t>Nếu cần plugin động: nạp vtable theo registry.</t>
   </si>
   <si>
-    <t>1.1.2 Builder Pattern (xây dựng đối tượng phức tạp từng bước, fluent API)</t>
-  </si>
-  <si>
     <t>struct XBuilder { X prod; XBuilder* (*set_a)(...,); ... X* (*build)(...); };</t>
   </si>
   <si>
@@ -595,9 +592,6 @@
   </si>
   <si>
     <t>Bẫy</t>
-  </si>
-  <si>
-    <t>1.1.3 Singleton Pattern (một instance toàn hệ)</t>
   </si>
   <si>
     <t>#include &lt;pthread.h&gt;</t>
@@ -3605,6 +3599,48 @@
       </rPr>
       <t xml:space="preserve"> mô phỏng exception (hiếm dùng, nguy hiểm).</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. tạo 1 typedef struct VTable chứa 2 con trỏ hàm đến hàm khởi tạo *create và hàm xóa đối tượng *delete; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Các obj từ struct Vtable sẽ có tên và được gán bằng các hàm khởi tạo và xóa cụ thể. </t>
+  </si>
+  <si>
+    <t>3. Tạo hàm Create để truyền tham số là sẽ chọn được kiểu obj trong danh sách các kiểu Vtable được khai báo trước, tương tự với delete</t>
+  </si>
+  <si>
+    <t>typedef struct Shape {</t>
+  </si>
+  <si>
+    <t>}Shape;</t>
+  </si>
+  <si>
+    <t>static void circle_draw(Shape* s) {}</t>
+  </si>
+  <si>
+    <t>static void circle_destroy(Shape* s) {}</t>
+  </si>
+  <si>
+    <t>static void rect_draw(Shape* s) {}</t>
+  </si>
+  <si>
+    <t>static void rect_destroy(Shape* s) {}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">// Create Circle obj. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">// Create Rect obj. </t>
+  </si>
+  <si>
+    <t>1.1.2 Singleton Pattern (một instance toàn hệ)</t>
+  </si>
+  <si>
+    <t>1.1.3 Builder Pattern (xây dựng đối tượng phức tạp từng bước, fluent API)</t>
+  </si>
+  <si>
+    <t>=&gt; đây là cách xây dựng Factory, Vtable ở đây khác với Vtable C++.</t>
   </si>
 </sst>
 </file>
@@ -3612,13 +3648,6 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="15">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3716,8 +3745,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3736,8 +3774,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3782,18 +3826,98 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3802,66 +3926,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4341,596 +4482,508 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CR203"/>
+  <dimension ref="A1:CN260"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3.125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" ht="15.75" thickBot="1">
+    <row r="1" spans="1:53" ht="15.75" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:96" s="19" customFormat="1" ht="15.75" thickBot="1">
+    <row r="2" spans="1:53" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A2" s="18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:96" ht="15">
+    <row r="3" spans="1:53" ht="15">
       <c r="A3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="W3" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="BK3" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="BL3" s="16"/>
-      <c r="BM3" s="16"/>
-      <c r="BN3" s="16"/>
-      <c r="BO3" s="16"/>
-      <c r="BP3" s="16"/>
-      <c r="BQ3" s="16"/>
-      <c r="BR3" s="16"/>
-      <c r="BS3" s="16"/>
-      <c r="BT3" s="16"/>
-      <c r="BU3" s="16"/>
-      <c r="BV3" s="16"/>
-      <c r="BW3" s="16"/>
-      <c r="BX3" s="16"/>
-      <c r="CR3" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:96" ht="15">
+      <c r="AN3" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="AO3" s="16"/>
+      <c r="AP3" s="16"/>
+      <c r="AQ3" s="16"/>
+      <c r="AR3" s="16"/>
+      <c r="AS3" s="16"/>
+      <c r="AT3" s="16"/>
+      <c r="AU3" s="16"/>
+      <c r="AV3" s="16"/>
+      <c r="AW3" s="16"/>
+      <c r="AX3" s="16"/>
+      <c r="AY3" s="16"/>
+      <c r="AZ3" s="16"/>
+      <c r="BA3" s="16"/>
+    </row>
+    <row r="4" spans="1:53" ht="15">
       <c r="A4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="V4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="BK4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="CR4" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:96" ht="15">
+    </row>
+    <row r="5" spans="1:53" ht="15">
       <c r="A5" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="BK5" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="CR5" s="11" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:96" ht="15">
+        <v>320</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53">
       <c r="A6" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="BK6" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="CR6" s="11" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:96" ht="15">
+        <v>321</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AN6" s="11" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53">
+      <c r="AE7" s="46"/>
+    </row>
+    <row r="8" spans="1:53" ht="15">
       <c r="A8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="W8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BK8" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="CR8" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:96">
+      <c r="V8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE8" s="20"/>
+      <c r="AN8" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" ht="15">
       <c r="A9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="W9" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK9" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="CR9" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:96">
+      <c r="V9" s="45" t="s">
+        <v>526</v>
+      </c>
+      <c r="W9" s="45"/>
+      <c r="AN9" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" ht="15">
       <c r="A10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="W10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK10" s="13" t="s">
+      <c r="V10" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="W10" s="45"/>
+      <c r="AN10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="CR10" s="13" t="s">
+    </row>
+    <row r="11" spans="1:53" ht="15">
+      <c r="A11" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="V11" s="45" t="s">
+        <v>527</v>
+      </c>
+      <c r="W11" s="45"/>
+      <c r="AN11" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:96">
-      <c r="A11" s="11" t="s">
+    <row r="12" spans="1:53">
+      <c r="A12" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN12" s="14"/>
+    </row>
+    <row r="13" spans="1:53">
+      <c r="V13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN13" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53" ht="15">
+      <c r="A14" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="BK11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="CR11" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:96" ht="15">
-      <c r="A12" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="BK12" s="14"/>
-      <c r="CR12" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:96">
-      <c r="W13" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="BK13" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="CR13" s="14"/>
-    </row>
-    <row r="14" spans="1:96" ht="15">
-      <c r="A14" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="W14" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="BK14" s="14"/>
-      <c r="CR14" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:96">
+      <c r="V14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN14" s="14"/>
+    </row>
+    <row r="15" spans="1:53">
       <c r="A15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="W15" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="BK15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="CR15" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:96">
+      <c r="V15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN15" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53">
       <c r="A16" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="W16" s="14"/>
-      <c r="BK16" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="CR16" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="17" spans="1:96">
+      <c r="V16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN16" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
       <c r="A17" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="W17" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="BK17" s="14"/>
-      <c r="CR17" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="18" spans="1:96">
+      <c r="AN17" s="14"/>
+    </row>
+    <row r="18" spans="1:40">
       <c r="A18" s="14"/>
-      <c r="W18" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="BK18" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="CR18" s="14"/>
-    </row>
-    <row r="19" spans="1:96">
+      <c r="V18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN18" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40">
       <c r="A19" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="W19" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK19" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="CR19" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" spans="1:96">
+      <c r="V19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN19" s="17" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40">
       <c r="A20" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="W20" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="BK20" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="CR20" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:96">
+      <c r="V20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN20" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40">
       <c r="A21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="W21" s="14"/>
-      <c r="BK21" s="13" t="s">
+      <c r="V21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN21" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="CR21" s="13" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:96">
+    </row>
+    <row r="22" spans="1:40">
       <c r="A22" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="W22" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK22" s="14"/>
-      <c r="CR22" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:96">
+      <c r="V22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN22" s="14"/>
+    </row>
+    <row r="23" spans="1:40">
       <c r="A23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="W23" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="BK23" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="CR23" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:96">
+      <c r="AN23" s="17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40">
       <c r="A24" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="W24" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="BK24" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="CR24" s="13" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="25" spans="1:96">
+      <c r="V24" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="AN24" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:40">
       <c r="A25" s="14"/>
-      <c r="W25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="BK25" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="CR25" s="13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:96">
+      <c r="V25" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="AN25" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40">
       <c r="A26" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="W26" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK26" s="13" t="s">
+      <c r="AN26" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="CR26" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:96">
+    </row>
+    <row r="27" spans="1:40" ht="15">
       <c r="A27" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="W27" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="BK27" s="14"/>
-      <c r="CR27" s="13" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:96">
+      <c r="V27" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN27" s="14"/>
+    </row>
+    <row r="28" spans="1:40">
       <c r="A28" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="W28" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="BK28" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="CR28" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:96">
+      <c r="V28" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AN28" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:40">
       <c r="A29" s="14"/>
-      <c r="W29" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="BK29" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="CR29" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:96">
+      <c r="V29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AN29" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40">
       <c r="A30" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="W30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK30" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="CR30" s="13" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31" spans="1:96">
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
+      <c r="AN30" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40">
       <c r="A31" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="W31" s="14"/>
-      <c r="BK31" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="CR31" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:96">
+      <c r="V31" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
+      <c r="AN31" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40">
       <c r="A32" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="W32" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BK32" s="13" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:96" ht="15">
+      <c r="V32" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE32" s="20"/>
+      <c r="AF32" s="20"/>
+      <c r="AN32" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40">
       <c r="A33" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="W33" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="BK33" s="13" t="s">
+      <c r="V33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="20"/>
+      <c r="AN33" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="CR33" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:96" ht="15">
+    </row>
+    <row r="34" spans="1:40">
       <c r="A34" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="W34" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CR34" s="8" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="35" spans="1:96" ht="15">
+      <c r="V34" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" ht="15">
       <c r="A35" s="14"/>
-      <c r="W35" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="BK35" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="CR35" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="36" spans="1:96" ht="15">
+      <c r="V35" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN35" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:40" ht="15">
       <c r="A36" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="W36" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK36" s="11" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:96">
+      <c r="AN36" s="11" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:40">
       <c r="A37" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="W37" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="BK37" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:96">
+      <c r="V37" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="AN37" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:40">
       <c r="A38" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="W38" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:96">
+      <c r="V38" s="9" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="39" spans="1:40" ht="15">
       <c r="A39" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="W39" s="13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:96">
+      <c r="V39" s="45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40">
       <c r="A40" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="W40" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:96">
+      <c r="V40" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40">
       <c r="A41" s="14"/>
-      <c r="W41" s="14"/>
-    </row>
-    <row r="42" spans="1:96">
+      <c r="V41" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40">
       <c r="A42" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="W42" s="13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:96">
+    </row>
+    <row r="43" spans="1:40">
       <c r="A43" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="W43" s="13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="44" spans="1:96">
+      <c r="V43" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:40">
       <c r="A44" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="W44" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="45" spans="1:96">
+      <c r="V44" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:40">
       <c r="A45" s="14"/>
-      <c r="W45" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="46" spans="1:96">
+    </row>
+    <row r="46" spans="1:40" ht="15">
       <c r="A46" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="W46" s="13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:96">
+      <c r="V46" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:40">
       <c r="A47" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="W47" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="48" spans="1:96">
+      <c r="V47" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:40">
       <c r="A48" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="W48" s="13" t="s">
-        <v>70</v>
+      <c r="W48" s="9" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="W49" s="14"/>
+      <c r="V49" s="9" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="W50" s="13" t="s">
-        <v>141</v>
+      <c r="V50" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="14"/>
-      <c r="W51" s="13" t="s">
-        <v>142</v>
+      <c r="W51" s="9" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="W52" s="13" t="s">
-        <v>143</v>
+      <c r="V52" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:23">
       <c r="A53" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="W53" s="13" t="s">
-        <v>144</v>
+      <c r="V53" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="W54" s="13" t="s">
-        <v>145</v>
+      <c r="V54" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="W55" s="13" t="s">
+      <c r="V55" s="9" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4939,1220 +4992,4790 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="15">
+    <row r="57" spans="1:23">
       <c r="A57" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="W57" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23" ht="15">
+      <c r="V57" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
       <c r="A58" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="W58" s="11" t="s">
-        <v>330</v>
+      <c r="V58" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="W59" s="11" t="s">
-        <v>331</v>
+      <c r="V59" s="9" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="14"/>
+      <c r="V60" s="9" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="13" t="s">
         <v>83</v>
       </c>
+      <c r="V61" s="9" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="13" t="s">
         <v>84</v>
       </c>
+      <c r="V62" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="14"/>
+      <c r="V63" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:57">
       <c r="A65" s="13" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="V65" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="W65" s="34"/>
+      <c r="X65" s="34"/>
+      <c r="Y65" s="34"/>
+      <c r="Z65" s="34"/>
+      <c r="AA65" s="34"/>
+      <c r="AB65" s="34"/>
+      <c r="AC65" s="34"/>
+      <c r="AD65" s="34"/>
+      <c r="AE65" s="34"/>
+      <c r="AF65" s="34"/>
+      <c r="AG65" s="34"/>
+      <c r="AH65" s="34"/>
+      <c r="AI65" s="34"/>
+      <c r="AJ65" s="34"/>
+      <c r="AK65" s="34"/>
+      <c r="AL65" s="34"/>
+      <c r="AM65" s="34"/>
+      <c r="AN65" s="34"/>
+      <c r="AO65" s="34"/>
+      <c r="AP65" s="34"/>
+      <c r="AQ65" s="34"/>
+      <c r="AR65" s="34"/>
+      <c r="AS65" s="34"/>
+      <c r="AT65" s="34"/>
+      <c r="AU65" s="34"/>
+      <c r="AV65" s="34"/>
+      <c r="AW65" s="34"/>
+      <c r="AX65" s="34"/>
+      <c r="AY65" s="34"/>
+      <c r="AZ65" s="34"/>
+      <c r="BA65" s="34"/>
+      <c r="BB65" s="34"/>
+      <c r="BC65" s="34"/>
+      <c r="BD65" s="34"/>
+      <c r="BE65" s="35"/>
+    </row>
+    <row r="66" spans="1:57">
       <c r="A66" s="13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="V66" s="36" t="s">
+        <v>524</v>
+      </c>
+      <c r="W66" s="37"/>
+      <c r="X66" s="37"/>
+      <c r="Y66" s="37"/>
+      <c r="Z66" s="37"/>
+      <c r="AA66" s="37"/>
+      <c r="AB66" s="37"/>
+      <c r="AC66" s="37"/>
+      <c r="AD66" s="37"/>
+      <c r="AE66" s="37"/>
+      <c r="AF66" s="37"/>
+      <c r="AG66" s="37"/>
+      <c r="AH66" s="37"/>
+      <c r="AI66" s="37"/>
+      <c r="AJ66" s="37"/>
+      <c r="AK66" s="37"/>
+      <c r="AL66" s="37"/>
+      <c r="AM66" s="37"/>
+      <c r="AN66" s="37"/>
+      <c r="AO66" s="37"/>
+      <c r="AP66" s="37"/>
+      <c r="AQ66" s="37"/>
+      <c r="AR66" s="37"/>
+      <c r="AS66" s="37"/>
+      <c r="AT66" s="37"/>
+      <c r="AU66" s="37"/>
+      <c r="AV66" s="37"/>
+      <c r="AW66" s="37"/>
+      <c r="AX66" s="37"/>
+      <c r="AY66" s="37"/>
+      <c r="AZ66" s="37"/>
+      <c r="BA66" s="37"/>
+      <c r="BB66" s="37"/>
+      <c r="BC66" s="37"/>
+      <c r="BD66" s="37"/>
+      <c r="BE66" s="38"/>
+    </row>
+    <row r="67" spans="1:57">
       <c r="A67" s="13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="V67" s="39" t="s">
+        <v>525</v>
+      </c>
+      <c r="W67" s="40"/>
+      <c r="X67" s="40"/>
+      <c r="Y67" s="40"/>
+      <c r="Z67" s="40"/>
+      <c r="AA67" s="40"/>
+      <c r="AB67" s="40"/>
+      <c r="AC67" s="40"/>
+      <c r="AD67" s="40"/>
+      <c r="AE67" s="40"/>
+      <c r="AF67" s="40"/>
+      <c r="AG67" s="40"/>
+      <c r="AH67" s="40"/>
+      <c r="AI67" s="40"/>
+      <c r="AJ67" s="40"/>
+      <c r="AK67" s="40"/>
+      <c r="AL67" s="40"/>
+      <c r="AM67" s="40"/>
+      <c r="AN67" s="40"/>
+      <c r="AO67" s="40"/>
+      <c r="AP67" s="40"/>
+      <c r="AQ67" s="40"/>
+      <c r="AR67" s="40"/>
+      <c r="AS67" s="40"/>
+      <c r="AT67" s="40"/>
+      <c r="AU67" s="40"/>
+      <c r="AV67" s="40"/>
+      <c r="AW67" s="40"/>
+      <c r="AX67" s="40"/>
+      <c r="AY67" s="40"/>
+      <c r="AZ67" s="40"/>
+      <c r="BA67" s="40"/>
+      <c r="BB67" s="40"/>
+      <c r="BC67" s="40"/>
+      <c r="BD67" s="40"/>
+      <c r="BE67" s="41"/>
+    </row>
+    <row r="68" spans="1:57" ht="15">
       <c r="A68" s="13" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="W68" s="47" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="69" spans="1:57">
       <c r="A69" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:57">
       <c r="A70" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:57">
       <c r="A71" s="13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:57">
       <c r="A72" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:57">
       <c r="A73" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:57">
       <c r="A74" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:57">
       <c r="A75" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:57">
       <c r="A76" s="13" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:57">
       <c r="A77" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:57">
       <c r="A78" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:57">
       <c r="A79" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:57">
       <c r="A80" s="13" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:55">
       <c r="A81" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:55">
       <c r="A82" s="13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:55">
       <c r="A83" s="14"/>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:55">
       <c r="A84" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:55">
       <c r="A85" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:55">
       <c r="A86" s="13" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:55">
       <c r="A87" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:55">
       <c r="A88" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:55">
       <c r="A89" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:55">
       <c r="A90" s="13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="15">
+    <row r="92" spans="1:55" ht="15">
       <c r="A92" s="7" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="15">
+    <row r="93" spans="1:55" ht="15">
       <c r="A93" s="11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="94" spans="1:55">
       <c r="A94" s="11" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:55">
       <c r="A95" s="11" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="15" thickBot="1">
-      <c r="A96" s="11"/>
-    </row>
-    <row r="97" spans="1:79" s="19" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A97" s="18" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="98" spans="1:79" ht="15">
-      <c r="A98" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB98" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="BC98" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="CA98" s="10" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="99" spans="1:79" ht="15">
-      <c r="A99" s="7" t="s">
+    <row r="96" spans="1:55" s="43" customFormat="1">
+      <c r="A96" s="42"/>
+      <c r="T96" s="44"/>
+      <c r="U96" s="44"/>
+      <c r="V96" s="44"/>
+      <c r="W96" s="44"/>
+      <c r="X96" s="44"/>
+      <c r="Y96" s="44"/>
+      <c r="Z96" s="44"/>
+      <c r="AA96" s="44"/>
+      <c r="AB96" s="44"/>
+      <c r="AC96" s="44"/>
+      <c r="AD96" s="44"/>
+      <c r="AE96" s="44"/>
+      <c r="AF96" s="44"/>
+      <c r="AG96" s="44"/>
+      <c r="AH96" s="44"/>
+      <c r="AI96" s="44"/>
+      <c r="AJ96" s="44"/>
+      <c r="AK96" s="44"/>
+      <c r="AL96" s="44"/>
+      <c r="AM96" s="44"/>
+      <c r="AN96" s="44"/>
+      <c r="AO96" s="44"/>
+      <c r="AP96" s="44"/>
+      <c r="AQ96" s="44"/>
+      <c r="AR96" s="44"/>
+      <c r="AS96" s="44"/>
+      <c r="AT96" s="44"/>
+      <c r="AU96" s="44"/>
+      <c r="AV96" s="44"/>
+      <c r="AW96" s="44"/>
+      <c r="AX96" s="44"/>
+      <c r="AY96" s="44"/>
+      <c r="AZ96" s="44"/>
+      <c r="BA96" s="44"/>
+      <c r="BB96" s="44"/>
+      <c r="BC96" s="44"/>
+    </row>
+    <row r="97" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A97" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="9"/>
+      <c r="M97" s="9"/>
+      <c r="N97" s="9"/>
+      <c r="O97" s="9"/>
+      <c r="P97" s="9"/>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+      <c r="S97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
+      <c r="V97" s="9"/>
+      <c r="W97" s="9"/>
+      <c r="X97" s="9"/>
+      <c r="Y97" s="9"/>
+      <c r="Z97" s="9"/>
+      <c r="AA97" s="9"/>
+      <c r="AB97" s="9"/>
+      <c r="AC97" s="9"/>
+      <c r="AD97" s="9"/>
+      <c r="AE97" s="9"/>
+      <c r="AF97" s="9"/>
+      <c r="AG97" s="9"/>
+      <c r="AH97" s="9"/>
+      <c r="AI97" s="9"/>
+      <c r="AJ97" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK97" s="9"/>
+      <c r="AL97" s="9"/>
+      <c r="AM97" s="9"/>
+      <c r="AN97" s="9"/>
+      <c r="AO97" s="9"/>
+      <c r="AP97" s="9"/>
+      <c r="AQ97" s="9"/>
+      <c r="AR97" s="9"/>
+      <c r="AS97" s="9"/>
+      <c r="AT97" s="9"/>
+      <c r="AU97" s="9"/>
+      <c r="AV97" s="9"/>
+      <c r="AW97" s="44"/>
+      <c r="AX97" s="44"/>
+      <c r="AY97" s="44"/>
+      <c r="AZ97" s="44"/>
+      <c r="BA97" s="44"/>
+      <c r="BB97" s="44"/>
+      <c r="BC97" s="44"/>
+    </row>
+    <row r="98" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A98" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AB99" s="7" t="s">
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+      <c r="N98" s="9"/>
+      <c r="O98" s="9"/>
+      <c r="P98" s="9"/>
+      <c r="Q98" s="9"/>
+      <c r="R98" s="9"/>
+      <c r="S98" s="9"/>
+      <c r="T98" s="9"/>
+      <c r="U98" s="9"/>
+      <c r="V98" s="9"/>
+      <c r="W98" s="9"/>
+      <c r="X98" s="9"/>
+      <c r="Y98" s="9"/>
+      <c r="Z98" s="9"/>
+      <c r="AA98" s="9"/>
+      <c r="AB98" s="9"/>
+      <c r="AC98" s="9"/>
+      <c r="AD98" s="9"/>
+      <c r="AE98" s="9"/>
+      <c r="AF98" s="9"/>
+      <c r="AG98" s="9"/>
+      <c r="AH98" s="9"/>
+      <c r="AI98" s="9"/>
+      <c r="AJ98" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="BC99" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="CA99" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="100" spans="1:79" ht="15">
-      <c r="A100" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB100" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="BC100" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="CA100" s="11" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="101" spans="1:79" ht="15">
-      <c r="AB101" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="BC101" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="CA101" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="102" spans="1:79" ht="15">
+      <c r="AK98" s="9"/>
+      <c r="AL98" s="9"/>
+      <c r="AM98" s="9"/>
+      <c r="AN98" s="9"/>
+      <c r="AO98" s="9"/>
+      <c r="AP98" s="9"/>
+      <c r="AQ98" s="9"/>
+      <c r="AR98" s="9"/>
+      <c r="AS98" s="9"/>
+      <c r="AT98" s="9"/>
+      <c r="AU98" s="9"/>
+      <c r="AV98" s="9"/>
+      <c r="AW98" s="44"/>
+      <c r="AX98" s="44"/>
+      <c r="AY98" s="44"/>
+      <c r="AZ98" s="44"/>
+      <c r="BA98" s="44"/>
+      <c r="BB98" s="44"/>
+      <c r="BC98" s="44"/>
+    </row>
+    <row r="99" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A99" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="9"/>
+      <c r="M99" s="9"/>
+      <c r="N99" s="9"/>
+      <c r="O99" s="9"/>
+      <c r="P99" s="9"/>
+      <c r="Q99" s="9"/>
+      <c r="R99" s="9"/>
+      <c r="S99" s="9"/>
+      <c r="T99" s="9"/>
+      <c r="U99" s="9"/>
+      <c r="V99" s="9"/>
+      <c r="W99" s="9"/>
+      <c r="X99" s="9"/>
+      <c r="Y99" s="9"/>
+      <c r="Z99" s="9"/>
+      <c r="AA99" s="9"/>
+      <c r="AB99" s="9"/>
+      <c r="AC99" s="9"/>
+      <c r="AD99" s="9"/>
+      <c r="AE99" s="9"/>
+      <c r="AF99" s="9"/>
+      <c r="AG99" s="9"/>
+      <c r="AH99" s="9"/>
+      <c r="AI99" s="9"/>
+      <c r="AJ99" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="AK99" s="9"/>
+      <c r="AL99" s="9"/>
+      <c r="AM99" s="9"/>
+      <c r="AN99" s="9"/>
+      <c r="AO99" s="9"/>
+      <c r="AP99" s="9"/>
+      <c r="AQ99" s="9"/>
+      <c r="AR99" s="9"/>
+      <c r="AS99" s="9"/>
+      <c r="AT99" s="9"/>
+      <c r="AU99" s="9"/>
+      <c r="AV99" s="9"/>
+      <c r="AW99" s="44"/>
+      <c r="AX99" s="44"/>
+      <c r="AY99" s="44"/>
+      <c r="AZ99" s="44"/>
+      <c r="BA99" s="44"/>
+      <c r="BB99" s="44"/>
+      <c r="BC99" s="44"/>
+    </row>
+    <row r="100" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A100" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+      <c r="N100" s="9"/>
+      <c r="O100" s="9"/>
+      <c r="P100" s="9"/>
+      <c r="Q100" s="9"/>
+      <c r="R100" s="9"/>
+      <c r="S100" s="9"/>
+      <c r="T100" s="9"/>
+      <c r="U100" s="9"/>
+      <c r="V100" s="9"/>
+      <c r="W100" s="9"/>
+      <c r="X100" s="9"/>
+      <c r="Y100" s="9"/>
+      <c r="Z100" s="9"/>
+      <c r="AA100" s="9"/>
+      <c r="AB100" s="9"/>
+      <c r="AC100" s="9"/>
+      <c r="AD100" s="9"/>
+      <c r="AE100" s="9"/>
+      <c r="AF100" s="9"/>
+      <c r="AG100" s="9"/>
+      <c r="AH100" s="9"/>
+      <c r="AI100" s="9"/>
+      <c r="AJ100" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="AK100" s="9"/>
+      <c r="AL100" s="9"/>
+      <c r="AM100" s="9"/>
+      <c r="AN100" s="9"/>
+      <c r="AO100" s="9"/>
+      <c r="AP100" s="9"/>
+      <c r="AQ100" s="9"/>
+      <c r="AR100" s="9"/>
+      <c r="AS100" s="9"/>
+      <c r="AT100" s="9"/>
+      <c r="AU100" s="9"/>
+      <c r="AV100" s="9"/>
+      <c r="AW100" s="44"/>
+      <c r="AX100" s="44"/>
+      <c r="AY100" s="44"/>
+      <c r="AZ100" s="44"/>
+      <c r="BA100" s="44"/>
+      <c r="BB100" s="44"/>
+      <c r="BC100" s="44"/>
+    </row>
+    <row r="101" spans="1:55" s="43" customFormat="1">
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+      <c r="N101" s="9"/>
+      <c r="O101" s="9"/>
+      <c r="P101" s="9"/>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
+      <c r="S101" s="9"/>
+      <c r="T101" s="9"/>
+      <c r="U101" s="9"/>
+      <c r="V101" s="9"/>
+      <c r="W101" s="9"/>
+      <c r="X101" s="9"/>
+      <c r="Y101" s="9"/>
+      <c r="Z101" s="9"/>
+      <c r="AA101" s="9"/>
+      <c r="AB101" s="9"/>
+      <c r="AC101" s="9"/>
+      <c r="AD101" s="9"/>
+      <c r="AE101" s="9"/>
+      <c r="AF101" s="9"/>
+      <c r="AG101" s="9"/>
+      <c r="AH101" s="9"/>
+      <c r="AI101" s="9"/>
+      <c r="AJ101" s="9"/>
+      <c r="AK101" s="9"/>
+      <c r="AL101" s="9"/>
+      <c r="AM101" s="9"/>
+      <c r="AN101" s="9"/>
+      <c r="AO101" s="9"/>
+      <c r="AP101" s="9"/>
+      <c r="AQ101" s="9"/>
+      <c r="AR101" s="9"/>
+      <c r="AS101" s="9"/>
+      <c r="AT101" s="9"/>
+      <c r="AU101" s="9"/>
+      <c r="AV101" s="9"/>
+      <c r="AW101" s="44"/>
+      <c r="AX101" s="44"/>
+      <c r="AY101" s="44"/>
+      <c r="AZ101" s="44"/>
+      <c r="BA101" s="44"/>
+      <c r="BB101" s="44"/>
+      <c r="BC101" s="44"/>
+    </row>
+    <row r="102" spans="1:55" s="43" customFormat="1" ht="15">
       <c r="A102" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="CA102" s="13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="103" spans="1:79" ht="15">
-      <c r="A103" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="9"/>
+      <c r="I102" s="9"/>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9"/>
+      <c r="L102" s="9"/>
+      <c r="M102" s="9"/>
+      <c r="N102" s="9"/>
+      <c r="O102" s="9"/>
+      <c r="P102" s="9"/>
+      <c r="Q102" s="9"/>
+      <c r="R102" s="9"/>
+      <c r="S102" s="9"/>
+      <c r="T102" s="9"/>
+      <c r="U102" s="9"/>
+      <c r="V102" s="9"/>
+      <c r="W102" s="9"/>
+      <c r="X102" s="9"/>
+      <c r="Y102" s="9"/>
+      <c r="Z102" s="9"/>
+      <c r="AA102" s="9"/>
+      <c r="AB102" s="9"/>
+      <c r="AC102" s="9"/>
+      <c r="AD102" s="9"/>
+      <c r="AE102" s="9"/>
+      <c r="AF102" s="9"/>
+      <c r="AG102" s="9"/>
+      <c r="AH102" s="9"/>
+      <c r="AI102" s="9"/>
+      <c r="AJ102" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="AK102" s="9"/>
+      <c r="AL102" s="9"/>
+      <c r="AM102" s="9"/>
+      <c r="AN102" s="9"/>
+      <c r="AO102" s="9"/>
+      <c r="AP102" s="9"/>
+      <c r="AQ102" s="9"/>
+      <c r="AR102" s="9"/>
+      <c r="AS102" s="9"/>
+      <c r="AT102" s="9"/>
+      <c r="AU102" s="9"/>
+      <c r="AV102" s="9"/>
+      <c r="AW102" s="44"/>
+      <c r="AX102" s="44"/>
+      <c r="AY102" s="44"/>
+      <c r="AZ102" s="44"/>
+      <c r="BA102" s="44"/>
+      <c r="BB102" s="44"/>
+      <c r="BC102" s="44"/>
+    </row>
+    <row r="103" spans="1:55" s="43" customFormat="1">
+      <c r="A103" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="9"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="9"/>
+      <c r="L103" s="9"/>
+      <c r="M103" s="9"/>
+      <c r="N103" s="9"/>
+      <c r="O103" s="9"/>
+      <c r="P103" s="9"/>
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
+      <c r="V103" s="9"/>
+      <c r="W103" s="9"/>
+      <c r="X103" s="9"/>
+      <c r="Y103" s="9"/>
+      <c r="Z103" s="9"/>
+      <c r="AA103" s="9"/>
+      <c r="AB103" s="9"/>
+      <c r="AC103" s="9"/>
+      <c r="AD103" s="9"/>
+      <c r="AE103" s="9"/>
+      <c r="AF103" s="9"/>
+      <c r="AG103" s="9"/>
+      <c r="AH103" s="9"/>
+      <c r="AI103" s="9"/>
+      <c r="AJ103" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK103" s="9"/>
+      <c r="AL103" s="9"/>
+      <c r="AM103" s="9"/>
+      <c r="AN103" s="9"/>
+      <c r="AO103" s="9"/>
+      <c r="AP103" s="9"/>
+      <c r="AQ103" s="9"/>
+      <c r="AR103" s="9"/>
+      <c r="AS103" s="9"/>
+      <c r="AT103" s="9"/>
+      <c r="AU103" s="9"/>
+      <c r="AV103" s="9"/>
+      <c r="AW103" s="44"/>
+      <c r="AX103" s="44"/>
+      <c r="AY103" s="44"/>
+      <c r="AZ103" s="44"/>
+      <c r="BA103" s="44"/>
+      <c r="BB103" s="44"/>
+      <c r="BC103" s="44"/>
+    </row>
+    <row r="104" spans="1:55" s="43" customFormat="1">
+      <c r="A104" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="9"/>
+      <c r="F104" s="9"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="9"/>
+      <c r="I104" s="9"/>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9"/>
+      <c r="L104" s="9"/>
+      <c r="M104" s="9"/>
+      <c r="N104" s="9"/>
+      <c r="O104" s="9"/>
+      <c r="P104" s="9"/>
+      <c r="Q104" s="9"/>
+      <c r="R104" s="9"/>
+      <c r="S104" s="9"/>
+      <c r="T104" s="9"/>
+      <c r="U104" s="9"/>
+      <c r="V104" s="9"/>
+      <c r="W104" s="9"/>
+      <c r="X104" s="9"/>
+      <c r="Y104" s="9"/>
+      <c r="Z104" s="9"/>
+      <c r="AA104" s="9"/>
+      <c r="AB104" s="9"/>
+      <c r="AC104" s="9"/>
+      <c r="AD104" s="9"/>
+      <c r="AE104" s="9"/>
+      <c r="AF104" s="9"/>
+      <c r="AG104" s="9"/>
+      <c r="AH104" s="9"/>
+      <c r="AI104" s="9"/>
+      <c r="AJ104" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AB103" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC103" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="CA103" s="13" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="104" spans="1:79">
-      <c r="A104" s="14"/>
-      <c r="AB104" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="BC104" s="13" t="s">
+      <c r="AK104" s="9"/>
+      <c r="AL104" s="9"/>
+      <c r="AM104" s="9"/>
+      <c r="AN104" s="9"/>
+      <c r="AO104" s="9"/>
+      <c r="AP104" s="9"/>
+      <c r="AQ104" s="9"/>
+      <c r="AR104" s="9"/>
+      <c r="AS104" s="9"/>
+      <c r="AT104" s="9"/>
+      <c r="AU104" s="9"/>
+      <c r="AV104" s="9"/>
+      <c r="AW104" s="44"/>
+      <c r="AX104" s="44"/>
+      <c r="AY104" s="44"/>
+      <c r="AZ104" s="44"/>
+      <c r="BA104" s="44"/>
+      <c r="BB104" s="44"/>
+      <c r="BC104" s="44"/>
+    </row>
+    <row r="105" spans="1:55" s="43" customFormat="1">
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="9"/>
+      <c r="F105" s="9"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9"/>
+      <c r="I105" s="9"/>
+      <c r="J105" s="9"/>
+      <c r="K105" s="9"/>
+      <c r="L105" s="9"/>
+      <c r="M105" s="9"/>
+      <c r="N105" s="9"/>
+      <c r="O105" s="9"/>
+      <c r="P105" s="9"/>
+      <c r="Q105" s="9"/>
+      <c r="R105" s="9"/>
+      <c r="S105" s="9"/>
+      <c r="T105" s="9"/>
+      <c r="U105" s="9"/>
+      <c r="V105" s="9"/>
+      <c r="W105" s="9"/>
+      <c r="X105" s="9"/>
+      <c r="Y105" s="9"/>
+      <c r="Z105" s="9"/>
+      <c r="AA105" s="9"/>
+      <c r="AB105" s="9"/>
+      <c r="AC105" s="9"/>
+      <c r="AD105" s="9"/>
+      <c r="AE105" s="9"/>
+      <c r="AF105" s="9"/>
+      <c r="AG105" s="9"/>
+      <c r="AH105" s="9"/>
+      <c r="AI105" s="9"/>
+      <c r="AJ105" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK105" s="9"/>
+      <c r="AL105" s="9"/>
+      <c r="AM105" s="9"/>
+      <c r="AN105" s="9"/>
+      <c r="AO105" s="9"/>
+      <c r="AP105" s="9"/>
+      <c r="AQ105" s="9"/>
+      <c r="AR105" s="9"/>
+      <c r="AS105" s="9"/>
+      <c r="AT105" s="9"/>
+      <c r="AU105" s="9"/>
+      <c r="AV105" s="9"/>
+      <c r="AW105" s="44"/>
+      <c r="AX105" s="44"/>
+      <c r="AY105" s="44"/>
+      <c r="AZ105" s="44"/>
+      <c r="BA105" s="44"/>
+      <c r="BB105" s="44"/>
+      <c r="BC105" s="44"/>
+    </row>
+    <row r="106" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A106" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="9"/>
+      <c r="M106" s="9"/>
+      <c r="N106" s="9"/>
+      <c r="O106" s="9"/>
+      <c r="P106" s="9"/>
+      <c r="Q106" s="9"/>
+      <c r="R106" s="9"/>
+      <c r="S106" s="9"/>
+      <c r="T106" s="9"/>
+      <c r="U106" s="9"/>
+      <c r="V106" s="9"/>
+      <c r="W106" s="9"/>
+      <c r="X106" s="9"/>
+      <c r="Y106" s="9"/>
+      <c r="Z106" s="9"/>
+      <c r="AA106" s="9"/>
+      <c r="AB106" s="9"/>
+      <c r="AC106" s="9"/>
+      <c r="AD106" s="9"/>
+      <c r="AE106" s="9"/>
+      <c r="AF106" s="9"/>
+      <c r="AG106" s="9"/>
+      <c r="AH106" s="9"/>
+      <c r="AI106" s="9"/>
+      <c r="AJ106" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK106" s="9"/>
+      <c r="AL106" s="9"/>
+      <c r="AM106" s="9"/>
+      <c r="AN106" s="9"/>
+      <c r="AO106" s="9"/>
+      <c r="AP106" s="9"/>
+      <c r="AQ106" s="9"/>
+      <c r="AR106" s="9"/>
+      <c r="AS106" s="9"/>
+      <c r="AT106" s="9"/>
+      <c r="AU106" s="9"/>
+      <c r="AV106" s="9"/>
+      <c r="AW106" s="44"/>
+      <c r="AX106" s="44"/>
+      <c r="AY106" s="44"/>
+      <c r="AZ106" s="44"/>
+      <c r="BA106" s="44"/>
+      <c r="BB106" s="44"/>
+      <c r="BC106" s="44"/>
+    </row>
+    <row r="107" spans="1:55" s="43" customFormat="1">
+      <c r="A107" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="CA104" s="13" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="105" spans="1:79">
-      <c r="A105" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB105" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="BC105" s="13" t="s">
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+      <c r="N107" s="9"/>
+      <c r="O107" s="9"/>
+      <c r="P107" s="9"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+      <c r="S107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
+      <c r="V107" s="9"/>
+      <c r="W107" s="9"/>
+      <c r="X107" s="9"/>
+      <c r="Y107" s="9"/>
+      <c r="Z107" s="9"/>
+      <c r="AA107" s="9"/>
+      <c r="AB107" s="9"/>
+      <c r="AC107" s="9"/>
+      <c r="AD107" s="9"/>
+      <c r="AE107" s="9"/>
+      <c r="AF107" s="9"/>
+      <c r="AG107" s="9"/>
+      <c r="AH107" s="9"/>
+      <c r="AI107" s="9"/>
+      <c r="AJ107" s="14"/>
+      <c r="AK107" s="9"/>
+      <c r="AL107" s="9"/>
+      <c r="AM107" s="9"/>
+      <c r="AN107" s="9"/>
+      <c r="AO107" s="9"/>
+      <c r="AP107" s="9"/>
+      <c r="AQ107" s="9"/>
+      <c r="AR107" s="9"/>
+      <c r="AS107" s="9"/>
+      <c r="AT107" s="9"/>
+      <c r="AU107" s="9"/>
+      <c r="AV107" s="9"/>
+      <c r="AW107" s="44"/>
+      <c r="AX107" s="44"/>
+      <c r="AY107" s="44"/>
+      <c r="AZ107" s="44"/>
+      <c r="BA107" s="44"/>
+      <c r="BB107" s="44"/>
+      <c r="BC107" s="44"/>
+    </row>
+    <row r="108" spans="1:55" s="43" customFormat="1">
+      <c r="A108" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="CA105" s="13" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="106" spans="1:79">
-      <c r="A106" s="14"/>
-      <c r="BC106" s="14"/>
-    </row>
-    <row r="107" spans="1:79" ht="15">
-      <c r="A107" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB107" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="BC107" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="CA107" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="108" spans="1:79" ht="15">
-      <c r="A108" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB108" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="BC108" s="13" t="s">
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+      <c r="G108" s="9"/>
+      <c r="H108" s="9"/>
+      <c r="I108" s="9"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9"/>
+      <c r="L108" s="9"/>
+      <c r="M108" s="9"/>
+      <c r="N108" s="9"/>
+      <c r="O108" s="9"/>
+      <c r="P108" s="9"/>
+      <c r="Q108" s="9"/>
+      <c r="R108" s="9"/>
+      <c r="S108" s="9"/>
+      <c r="T108" s="9"/>
+      <c r="U108" s="9"/>
+      <c r="V108" s="9"/>
+      <c r="W108" s="9"/>
+      <c r="X108" s="9"/>
+      <c r="Y108" s="9"/>
+      <c r="Z108" s="9"/>
+      <c r="AA108" s="9"/>
+      <c r="AB108" s="9"/>
+      <c r="AC108" s="9"/>
+      <c r="AD108" s="9"/>
+      <c r="AE108" s="9"/>
+      <c r="AF108" s="9"/>
+      <c r="AG108" s="9"/>
+      <c r="AH108" s="9"/>
+      <c r="AI108" s="9"/>
+      <c r="AJ108" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK108" s="9"/>
+      <c r="AL108" s="9"/>
+      <c r="AM108" s="9"/>
+      <c r="AN108" s="9"/>
+      <c r="AO108" s="9"/>
+      <c r="AP108" s="9"/>
+      <c r="AQ108" s="9"/>
+      <c r="AR108" s="9"/>
+      <c r="AS108" s="9"/>
+      <c r="AT108" s="9"/>
+      <c r="AU108" s="9"/>
+      <c r="AV108" s="9"/>
+      <c r="AW108" s="44"/>
+      <c r="AX108" s="44"/>
+      <c r="AY108" s="44"/>
+      <c r="AZ108" s="44"/>
+      <c r="BA108" s="44"/>
+      <c r="BB108" s="44"/>
+      <c r="BC108" s="44"/>
+    </row>
+    <row r="109" spans="1:55" s="43" customFormat="1">
+      <c r="A109" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
+      <c r="K109" s="9"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+      <c r="N109" s="9"/>
+      <c r="O109" s="9"/>
+      <c r="P109" s="9"/>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
+      <c r="V109" s="9"/>
+      <c r="W109" s="9"/>
+      <c r="X109" s="9"/>
+      <c r="Y109" s="9"/>
+      <c r="Z109" s="9"/>
+      <c r="AA109" s="9"/>
+      <c r="AB109" s="9"/>
+      <c r="AC109" s="9"/>
+      <c r="AD109" s="9"/>
+      <c r="AE109" s="9"/>
+      <c r="AF109" s="9"/>
+      <c r="AG109" s="9"/>
+      <c r="AH109" s="9"/>
+      <c r="AI109" s="9"/>
+      <c r="AJ109" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK109" s="9"/>
+      <c r="AL109" s="9"/>
+      <c r="AM109" s="9"/>
+      <c r="AN109" s="9"/>
+      <c r="AO109" s="9"/>
+      <c r="AP109" s="9"/>
+      <c r="AQ109" s="9"/>
+      <c r="AR109" s="9"/>
+      <c r="AS109" s="9"/>
+      <c r="AT109" s="9"/>
+      <c r="AU109" s="9"/>
+      <c r="AV109" s="9"/>
+      <c r="AW109" s="44"/>
+      <c r="AX109" s="44"/>
+      <c r="AY109" s="44"/>
+      <c r="AZ109" s="44"/>
+      <c r="BA109" s="44"/>
+      <c r="BB109" s="44"/>
+      <c r="BC109" s="44"/>
+    </row>
+    <row r="110" spans="1:55" s="43" customFormat="1">
+      <c r="A110" s="14"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="9"/>
+      <c r="K110" s="9"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+      <c r="N110" s="9"/>
+      <c r="O110" s="9"/>
+      <c r="P110" s="9"/>
+      <c r="Q110" s="9"/>
+      <c r="R110" s="9"/>
+      <c r="S110" s="9"/>
+      <c r="T110" s="9"/>
+      <c r="U110" s="9"/>
+      <c r="V110" s="9"/>
+      <c r="W110" s="9"/>
+      <c r="X110" s="9"/>
+      <c r="Y110" s="9"/>
+      <c r="Z110" s="9"/>
+      <c r="AA110" s="9"/>
+      <c r="AB110" s="9"/>
+      <c r="AC110" s="9"/>
+      <c r="AD110" s="9"/>
+      <c r="AE110" s="9"/>
+      <c r="AF110" s="9"/>
+      <c r="AG110" s="9"/>
+      <c r="AH110" s="9"/>
+      <c r="AI110" s="9"/>
+      <c r="AJ110" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK110" s="9"/>
+      <c r="AL110" s="9"/>
+      <c r="AM110" s="9"/>
+      <c r="AN110" s="9"/>
+      <c r="AO110" s="9"/>
+      <c r="AP110" s="9"/>
+      <c r="AQ110" s="9"/>
+      <c r="AR110" s="9"/>
+      <c r="AS110" s="9"/>
+      <c r="AT110" s="9"/>
+      <c r="AU110" s="9"/>
+      <c r="AV110" s="9"/>
+      <c r="AW110" s="44"/>
+      <c r="AX110" s="44"/>
+      <c r="AY110" s="44"/>
+      <c r="AZ110" s="44"/>
+      <c r="BA110" s="44"/>
+      <c r="BB110" s="44"/>
+      <c r="BC110" s="44"/>
+    </row>
+    <row r="111" spans="1:55" s="43" customFormat="1">
+      <c r="A111" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CA108" s="11" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="109" spans="1:79">
-      <c r="A109" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB109" s="14"/>
-      <c r="BC109" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="110" spans="1:79">
-      <c r="A110" s="14"/>
-      <c r="AB110" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="BC110" s="13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="111" spans="1:79">
-      <c r="A111" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB111" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="BC111" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="112" spans="1:79">
-      <c r="A112" s="14"/>
-      <c r="AB112" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="BC112" s="13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="113" spans="1:55">
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
+      <c r="F111" s="9"/>
+      <c r="G111" s="9"/>
+      <c r="H111" s="9"/>
+      <c r="I111" s="9"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9"/>
+      <c r="L111" s="9"/>
+      <c r="M111" s="9"/>
+      <c r="N111" s="9"/>
+      <c r="O111" s="9"/>
+      <c r="P111" s="9"/>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+      <c r="S111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
+      <c r="V111" s="9"/>
+      <c r="W111" s="9"/>
+      <c r="X111" s="9"/>
+      <c r="Y111" s="9"/>
+      <c r="Z111" s="9"/>
+      <c r="AA111" s="9"/>
+      <c r="AB111" s="9"/>
+      <c r="AC111" s="9"/>
+      <c r="AD111" s="9"/>
+      <c r="AE111" s="9"/>
+      <c r="AF111" s="9"/>
+      <c r="AG111" s="9"/>
+      <c r="AH111" s="9"/>
+      <c r="AI111" s="9"/>
+      <c r="AJ111" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK111" s="9"/>
+      <c r="AL111" s="9"/>
+      <c r="AM111" s="9"/>
+      <c r="AN111" s="9"/>
+      <c r="AO111" s="9"/>
+      <c r="AP111" s="9"/>
+      <c r="AQ111" s="9"/>
+      <c r="AR111" s="9"/>
+      <c r="AS111" s="9"/>
+      <c r="AT111" s="9"/>
+      <c r="AU111" s="9"/>
+      <c r="AV111" s="9"/>
+      <c r="AW111" s="44"/>
+      <c r="AX111" s="44"/>
+      <c r="AY111" s="44"/>
+      <c r="AZ111" s="44"/>
+      <c r="BA111" s="44"/>
+      <c r="BB111" s="44"/>
+      <c r="BC111" s="44"/>
+    </row>
+    <row r="112" spans="1:55" s="43" customFormat="1">
+      <c r="A112" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
+      <c r="N112" s="9"/>
+      <c r="O112" s="9"/>
+      <c r="P112" s="9"/>
+      <c r="Q112" s="9"/>
+      <c r="R112" s="9"/>
+      <c r="S112" s="9"/>
+      <c r="T112" s="9"/>
+      <c r="U112" s="9"/>
+      <c r="V112" s="9"/>
+      <c r="W112" s="9"/>
+      <c r="X112" s="9"/>
+      <c r="Y112" s="9"/>
+      <c r="Z112" s="9"/>
+      <c r="AA112" s="9"/>
+      <c r="AB112" s="9"/>
+      <c r="AC112" s="9"/>
+      <c r="AD112" s="9"/>
+      <c r="AE112" s="9"/>
+      <c r="AF112" s="9"/>
+      <c r="AG112" s="9"/>
+      <c r="AH112" s="9"/>
+      <c r="AI112" s="9"/>
+      <c r="AJ112" s="14"/>
+      <c r="AK112" s="9"/>
+      <c r="AL112" s="9"/>
+      <c r="AM112" s="9"/>
+      <c r="AN112" s="9"/>
+      <c r="AO112" s="9"/>
+      <c r="AP112" s="9"/>
+      <c r="AQ112" s="9"/>
+      <c r="AR112" s="9"/>
+      <c r="AS112" s="9"/>
+      <c r="AT112" s="9"/>
+      <c r="AU112" s="9"/>
+      <c r="AV112" s="9"/>
+      <c r="AW112" s="44"/>
+      <c r="AX112" s="44"/>
+      <c r="AY112" s="44"/>
+      <c r="AZ112" s="44"/>
+      <c r="BA112" s="44"/>
+      <c r="BB112" s="44"/>
+      <c r="BC112" s="44"/>
+    </row>
+    <row r="113" spans="1:55" s="43" customFormat="1">
       <c r="A113" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB113" s="14"/>
-      <c r="BC113" s="14"/>
-    </row>
-    <row r="114" spans="1:55">
+        <v>116</v>
+      </c>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9"/>
+      <c r="L113" s="9"/>
+      <c r="M113" s="9"/>
+      <c r="N113" s="9"/>
+      <c r="O113" s="9"/>
+      <c r="P113" s="9"/>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
+      <c r="V113" s="9"/>
+      <c r="W113" s="9"/>
+      <c r="X113" s="9"/>
+      <c r="Y113" s="9"/>
+      <c r="Z113" s="9"/>
+      <c r="AA113" s="9"/>
+      <c r="AB113" s="9"/>
+      <c r="AC113" s="9"/>
+      <c r="AD113" s="9"/>
+      <c r="AE113" s="9"/>
+      <c r="AF113" s="9"/>
+      <c r="AG113" s="9"/>
+      <c r="AH113" s="9"/>
+      <c r="AI113" s="9"/>
+      <c r="AJ113" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK113" s="9"/>
+      <c r="AL113" s="9"/>
+      <c r="AM113" s="9"/>
+      <c r="AN113" s="9"/>
+      <c r="AO113" s="9"/>
+      <c r="AP113" s="9"/>
+      <c r="AQ113" s="9"/>
+      <c r="AR113" s="9"/>
+      <c r="AS113" s="9"/>
+      <c r="AT113" s="9"/>
+      <c r="AU113" s="9"/>
+      <c r="AV113" s="9"/>
+      <c r="AW113" s="44"/>
+      <c r="AX113" s="44"/>
+      <c r="AY113" s="44"/>
+      <c r="AZ113" s="44"/>
+      <c r="BA113" s="44"/>
+      <c r="BB113" s="44"/>
+      <c r="BC113" s="44"/>
+    </row>
+    <row r="114" spans="1:55" s="43" customFormat="1">
       <c r="A114" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB114" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="BC114" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="115" spans="1:55">
-      <c r="A115" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB115" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="BC115" s="14"/>
-    </row>
-    <row r="116" spans="1:55">
+        <v>117</v>
+      </c>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="9"/>
+      <c r="F114" s="9"/>
+      <c r="G114" s="9"/>
+      <c r="H114" s="9"/>
+      <c r="I114" s="9"/>
+      <c r="J114" s="9"/>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9"/>
+      <c r="M114" s="9"/>
+      <c r="N114" s="9"/>
+      <c r="O114" s="9"/>
+      <c r="P114" s="9"/>
+      <c r="Q114" s="9"/>
+      <c r="R114" s="9"/>
+      <c r="S114" s="9"/>
+      <c r="T114" s="9"/>
+      <c r="U114" s="9"/>
+      <c r="V114" s="9"/>
+      <c r="W114" s="9"/>
+      <c r="X114" s="9"/>
+      <c r="Y114" s="9"/>
+      <c r="Z114" s="9"/>
+      <c r="AA114" s="9"/>
+      <c r="AB114" s="9"/>
+      <c r="AC114" s="9"/>
+      <c r="AD114" s="9"/>
+      <c r="AE114" s="9"/>
+      <c r="AF114" s="9"/>
+      <c r="AG114" s="9"/>
+      <c r="AH114" s="9"/>
+      <c r="AI114" s="9"/>
+      <c r="AJ114" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK114" s="9"/>
+      <c r="AL114" s="9"/>
+      <c r="AM114" s="9"/>
+      <c r="AN114" s="9"/>
+      <c r="AO114" s="9"/>
+      <c r="AP114" s="9"/>
+      <c r="AQ114" s="9"/>
+      <c r="AR114" s="9"/>
+      <c r="AS114" s="9"/>
+      <c r="AT114" s="9"/>
+      <c r="AU114" s="9"/>
+      <c r="AV114" s="9"/>
+      <c r="AW114" s="44"/>
+      <c r="AX114" s="44"/>
+      <c r="AY114" s="44"/>
+      <c r="AZ114" s="44"/>
+      <c r="BA114" s="44"/>
+      <c r="BB114" s="44"/>
+      <c r="BC114" s="44"/>
+    </row>
+    <row r="115" spans="1:55" s="43" customFormat="1">
+      <c r="A115" s="14"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="9"/>
+      <c r="F115" s="9"/>
+      <c r="G115" s="9"/>
+      <c r="H115" s="9"/>
+      <c r="I115" s="9"/>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9"/>
+      <c r="L115" s="9"/>
+      <c r="M115" s="9"/>
+      <c r="N115" s="9"/>
+      <c r="O115" s="9"/>
+      <c r="P115" s="9"/>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
+      <c r="V115" s="9"/>
+      <c r="W115" s="9"/>
+      <c r="X115" s="9"/>
+      <c r="Y115" s="9"/>
+      <c r="Z115" s="9"/>
+      <c r="AA115" s="9"/>
+      <c r="AB115" s="9"/>
+      <c r="AC115" s="9"/>
+      <c r="AD115" s="9"/>
+      <c r="AE115" s="9"/>
+      <c r="AF115" s="9"/>
+      <c r="AG115" s="9"/>
+      <c r="AH115" s="9"/>
+      <c r="AI115" s="9"/>
+      <c r="AJ115" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK115" s="9"/>
+      <c r="AL115" s="9"/>
+      <c r="AM115" s="9"/>
+      <c r="AN115" s="9"/>
+      <c r="AO115" s="9"/>
+      <c r="AP115" s="9"/>
+      <c r="AQ115" s="9"/>
+      <c r="AR115" s="9"/>
+      <c r="AS115" s="9"/>
+      <c r="AT115" s="9"/>
+      <c r="AU115" s="9"/>
+      <c r="AV115" s="9"/>
+      <c r="AW115" s="44"/>
+      <c r="AX115" s="44"/>
+      <c r="AY115" s="44"/>
+      <c r="AZ115" s="44"/>
+      <c r="BA115" s="44"/>
+      <c r="BB115" s="44"/>
+      <c r="BC115" s="44"/>
+    </row>
+    <row r="116" spans="1:55" s="43" customFormat="1">
       <c r="A116" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="9"/>
+      <c r="F116" s="9"/>
+      <c r="G116" s="9"/>
+      <c r="H116" s="9"/>
+      <c r="I116" s="9"/>
+      <c r="J116" s="9"/>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9"/>
+      <c r="M116" s="9"/>
+      <c r="N116" s="9"/>
+      <c r="O116" s="9"/>
+      <c r="P116" s="9"/>
+      <c r="Q116" s="9"/>
+      <c r="R116" s="9"/>
+      <c r="S116" s="9"/>
+      <c r="T116" s="9"/>
+      <c r="U116" s="9"/>
+      <c r="V116" s="9"/>
+      <c r="W116" s="9"/>
+      <c r="X116" s="9"/>
+      <c r="Y116" s="9"/>
+      <c r="Z116" s="9"/>
+      <c r="AA116" s="9"/>
+      <c r="AB116" s="9"/>
+      <c r="AC116" s="9"/>
+      <c r="AD116" s="9"/>
+      <c r="AE116" s="9"/>
+      <c r="AF116" s="9"/>
+      <c r="AG116" s="9"/>
+      <c r="AH116" s="9"/>
+      <c r="AI116" s="9"/>
+      <c r="AJ116" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK116" s="9"/>
+      <c r="AL116" s="9"/>
+      <c r="AM116" s="9"/>
+      <c r="AN116" s="9"/>
+      <c r="AO116" s="9"/>
+      <c r="AP116" s="9"/>
+      <c r="AQ116" s="9"/>
+      <c r="AR116" s="9"/>
+      <c r="AS116" s="9"/>
+      <c r="AT116" s="9"/>
+      <c r="AU116" s="9"/>
+      <c r="AV116" s="9"/>
+      <c r="AW116" s="44"/>
+      <c r="AX116" s="44"/>
+      <c r="AY116" s="44"/>
+      <c r="AZ116" s="44"/>
+      <c r="BA116" s="44"/>
+      <c r="BB116" s="44"/>
+      <c r="BC116" s="44"/>
+    </row>
+    <row r="117" spans="1:55" s="43" customFormat="1">
+      <c r="A117" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
+      <c r="E117" s="9"/>
+      <c r="F117" s="9"/>
+      <c r="G117" s="9"/>
+      <c r="H117" s="9"/>
+      <c r="I117" s="9"/>
+      <c r="J117" s="9"/>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9"/>
+      <c r="M117" s="9"/>
+      <c r="N117" s="9"/>
+      <c r="O117" s="9"/>
+      <c r="P117" s="9"/>
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+      <c r="S117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
+      <c r="V117" s="9"/>
+      <c r="W117" s="9"/>
+      <c r="X117" s="9"/>
+      <c r="Y117" s="9"/>
+      <c r="Z117" s="9"/>
+      <c r="AA117" s="9"/>
+      <c r="AB117" s="9"/>
+      <c r="AC117" s="9"/>
+      <c r="AD117" s="9"/>
+      <c r="AE117" s="9"/>
+      <c r="AF117" s="9"/>
+      <c r="AG117" s="9"/>
+      <c r="AH117" s="9"/>
+      <c r="AI117" s="9"/>
+      <c r="AJ117" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK117" s="9"/>
+      <c r="AL117" s="9"/>
+      <c r="AM117" s="9"/>
+      <c r="AN117" s="9"/>
+      <c r="AO117" s="9"/>
+      <c r="AP117" s="9"/>
+      <c r="AQ117" s="9"/>
+      <c r="AR117" s="9"/>
+      <c r="AS117" s="9"/>
+      <c r="AT117" s="9"/>
+      <c r="AU117" s="9"/>
+      <c r="AV117" s="9"/>
+      <c r="AW117" s="44"/>
+      <c r="AX117" s="44"/>
+      <c r="AY117" s="44"/>
+      <c r="AZ117" s="44"/>
+      <c r="BA117" s="44"/>
+      <c r="BB117" s="44"/>
+      <c r="BC117" s="44"/>
+    </row>
+    <row r="118" spans="1:55" s="43" customFormat="1">
+      <c r="A118" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="9"/>
+      <c r="F118" s="9"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="9"/>
+      <c r="I118" s="9"/>
+      <c r="J118" s="9"/>
+      <c r="K118" s="9"/>
+      <c r="L118" s="9"/>
+      <c r="M118" s="9"/>
+      <c r="N118" s="9"/>
+      <c r="O118" s="9"/>
+      <c r="P118" s="9"/>
+      <c r="Q118" s="9"/>
+      <c r="R118" s="9"/>
+      <c r="S118" s="9"/>
+      <c r="T118" s="9"/>
+      <c r="U118" s="9"/>
+      <c r="V118" s="9"/>
+      <c r="W118" s="9"/>
+      <c r="X118" s="9"/>
+      <c r="Y118" s="9"/>
+      <c r="Z118" s="9"/>
+      <c r="AA118" s="9"/>
+      <c r="AB118" s="9"/>
+      <c r="AC118" s="9"/>
+      <c r="AD118" s="9"/>
+      <c r="AE118" s="9"/>
+      <c r="AF118" s="9"/>
+      <c r="AG118" s="9"/>
+      <c r="AH118" s="9"/>
+      <c r="AI118" s="9"/>
+      <c r="AJ118" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK118" s="9"/>
+      <c r="AL118" s="9"/>
+      <c r="AM118" s="9"/>
+      <c r="AN118" s="9"/>
+      <c r="AO118" s="9"/>
+      <c r="AP118" s="9"/>
+      <c r="AQ118" s="9"/>
+      <c r="AR118" s="9"/>
+      <c r="AS118" s="9"/>
+      <c r="AT118" s="9"/>
+      <c r="AU118" s="9"/>
+      <c r="AV118" s="9"/>
+      <c r="AW118" s="44"/>
+      <c r="AX118" s="44"/>
+      <c r="AY118" s="44"/>
+      <c r="AZ118" s="44"/>
+      <c r="BA118" s="44"/>
+      <c r="BB118" s="44"/>
+      <c r="BC118" s="44"/>
+    </row>
+    <row r="119" spans="1:55" s="43" customFormat="1">
+      <c r="A119" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9"/>
+      <c r="G119" s="9"/>
+      <c r="H119" s="9"/>
+      <c r="I119" s="9"/>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9"/>
+      <c r="L119" s="9"/>
+      <c r="M119" s="9"/>
+      <c r="N119" s="9"/>
+      <c r="O119" s="9"/>
+      <c r="P119" s="9"/>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
+      <c r="V119" s="9"/>
+      <c r="W119" s="9"/>
+      <c r="X119" s="9"/>
+      <c r="Y119" s="9"/>
+      <c r="Z119" s="9"/>
+      <c r="AA119" s="9"/>
+      <c r="AB119" s="9"/>
+      <c r="AC119" s="9"/>
+      <c r="AD119" s="9"/>
+      <c r="AE119" s="9"/>
+      <c r="AF119" s="9"/>
+      <c r="AG119" s="9"/>
+      <c r="AH119" s="9"/>
+      <c r="AI119" s="9"/>
+      <c r="AJ119" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK119" s="9"/>
+      <c r="AL119" s="9"/>
+      <c r="AM119" s="9"/>
+      <c r="AN119" s="9"/>
+      <c r="AO119" s="9"/>
+      <c r="AP119" s="9"/>
+      <c r="AQ119" s="9"/>
+      <c r="AR119" s="9"/>
+      <c r="AS119" s="9"/>
+      <c r="AT119" s="9"/>
+      <c r="AU119" s="9"/>
+      <c r="AV119" s="9"/>
+      <c r="AW119" s="44"/>
+      <c r="AX119" s="44"/>
+      <c r="AY119" s="44"/>
+      <c r="AZ119" s="44"/>
+      <c r="BA119" s="44"/>
+      <c r="BB119" s="44"/>
+      <c r="BC119" s="44"/>
+    </row>
+    <row r="120" spans="1:55" s="43" customFormat="1">
+      <c r="A120" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
+      <c r="E120" s="9"/>
+      <c r="F120" s="9"/>
+      <c r="G120" s="9"/>
+      <c r="H120" s="9"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="9"/>
+      <c r="N120" s="9"/>
+      <c r="O120" s="9"/>
+      <c r="P120" s="9"/>
+      <c r="Q120" s="9"/>
+      <c r="R120" s="9"/>
+      <c r="S120" s="9"/>
+      <c r="T120" s="9"/>
+      <c r="U120" s="9"/>
+      <c r="V120" s="9"/>
+      <c r="W120" s="9"/>
+      <c r="X120" s="9"/>
+      <c r="Y120" s="9"/>
+      <c r="Z120" s="9"/>
+      <c r="AA120" s="9"/>
+      <c r="AB120" s="9"/>
+      <c r="AC120" s="9"/>
+      <c r="AD120" s="9"/>
+      <c r="AE120" s="9"/>
+      <c r="AF120" s="9"/>
+      <c r="AG120" s="9"/>
+      <c r="AH120" s="9"/>
+      <c r="AI120" s="9"/>
+      <c r="AJ120" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AB116" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="BC116" s="13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="117" spans="1:55">
-      <c r="A117" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB117" s="13" t="s">
+      <c r="AK120" s="9"/>
+      <c r="AL120" s="9"/>
+      <c r="AM120" s="9"/>
+      <c r="AN120" s="9"/>
+      <c r="AO120" s="9"/>
+      <c r="AP120" s="9"/>
+      <c r="AQ120" s="9"/>
+      <c r="AR120" s="9"/>
+      <c r="AS120" s="9"/>
+      <c r="AT120" s="9"/>
+      <c r="AU120" s="9"/>
+      <c r="AV120" s="9"/>
+      <c r="AW120" s="44"/>
+      <c r="AX120" s="44"/>
+      <c r="AY120" s="44"/>
+      <c r="AZ120" s="44"/>
+      <c r="BA120" s="44"/>
+      <c r="BB120" s="44"/>
+      <c r="BC120" s="44"/>
+    </row>
+    <row r="121" spans="1:55" s="43" customFormat="1">
+      <c r="A121" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9"/>
+      <c r="G121" s="9"/>
+      <c r="H121" s="9"/>
+      <c r="I121" s="9"/>
+      <c r="J121" s="9"/>
+      <c r="K121" s="9"/>
+      <c r="L121" s="9"/>
+      <c r="M121" s="9"/>
+      <c r="N121" s="9"/>
+      <c r="O121" s="9"/>
+      <c r="P121" s="9"/>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="9"/>
+      <c r="S121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
+      <c r="V121" s="9"/>
+      <c r="W121" s="9"/>
+      <c r="X121" s="9"/>
+      <c r="Y121" s="9"/>
+      <c r="Z121" s="9"/>
+      <c r="AA121" s="9"/>
+      <c r="AB121" s="9"/>
+      <c r="AC121" s="9"/>
+      <c r="AD121" s="9"/>
+      <c r="AE121" s="9"/>
+      <c r="AF121" s="9"/>
+      <c r="AG121" s="9"/>
+      <c r="AH121" s="9"/>
+      <c r="AI121" s="9"/>
+      <c r="AJ121" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK121" s="9"/>
+      <c r="AL121" s="9"/>
+      <c r="AM121" s="9"/>
+      <c r="AN121" s="9"/>
+      <c r="AO121" s="9"/>
+      <c r="AP121" s="9"/>
+      <c r="AQ121" s="9"/>
+      <c r="AR121" s="9"/>
+      <c r="AS121" s="9"/>
+      <c r="AT121" s="9"/>
+      <c r="AU121" s="9"/>
+      <c r="AV121" s="9"/>
+      <c r="AW121" s="44"/>
+      <c r="AX121" s="44"/>
+      <c r="AY121" s="44"/>
+      <c r="AZ121" s="44"/>
+      <c r="BA121" s="44"/>
+      <c r="BB121" s="44"/>
+      <c r="BC121" s="44"/>
+    </row>
+    <row r="122" spans="1:55" s="43" customFormat="1">
+      <c r="A122" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9"/>
+      <c r="G122" s="9"/>
+      <c r="H122" s="9"/>
+      <c r="I122" s="9"/>
+      <c r="J122" s="9"/>
+      <c r="K122" s="9"/>
+      <c r="L122" s="9"/>
+      <c r="M122" s="9"/>
+      <c r="N122" s="9"/>
+      <c r="O122" s="9"/>
+      <c r="P122" s="9"/>
+      <c r="Q122" s="9"/>
+      <c r="R122" s="9"/>
+      <c r="S122" s="9"/>
+      <c r="T122" s="9"/>
+      <c r="U122" s="9"/>
+      <c r="V122" s="9"/>
+      <c r="W122" s="9"/>
+      <c r="X122" s="9"/>
+      <c r="Y122" s="9"/>
+      <c r="Z122" s="9"/>
+      <c r="AA122" s="9"/>
+      <c r="AB122" s="9"/>
+      <c r="AC122" s="9"/>
+      <c r="AD122" s="9"/>
+      <c r="AE122" s="9"/>
+      <c r="AF122" s="9"/>
+      <c r="AG122" s="9"/>
+      <c r="AH122" s="9"/>
+      <c r="AI122" s="9"/>
+      <c r="AJ122" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK122" s="9"/>
+      <c r="AL122" s="9"/>
+      <c r="AM122" s="9"/>
+      <c r="AN122" s="9"/>
+      <c r="AO122" s="9"/>
+      <c r="AP122" s="9"/>
+      <c r="AQ122" s="9"/>
+      <c r="AR122" s="9"/>
+      <c r="AS122" s="9"/>
+      <c r="AT122" s="9"/>
+      <c r="AU122" s="9"/>
+      <c r="AV122" s="9"/>
+      <c r="AW122" s="44"/>
+      <c r="AX122" s="44"/>
+      <c r="AY122" s="44"/>
+      <c r="AZ122" s="44"/>
+      <c r="BA122" s="44"/>
+      <c r="BB122" s="44"/>
+      <c r="BC122" s="44"/>
+    </row>
+    <row r="123" spans="1:55" s="43" customFormat="1">
+      <c r="A123" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9"/>
+      <c r="O123" s="9"/>
+      <c r="P123" s="9"/>
+      <c r="Q123" s="9"/>
+      <c r="R123" s="9"/>
+      <c r="S123" s="9"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
+      <c r="V123" s="9"/>
+      <c r="W123" s="9"/>
+      <c r="X123" s="9"/>
+      <c r="Y123" s="9"/>
+      <c r="Z123" s="9"/>
+      <c r="AA123" s="9"/>
+      <c r="AB123" s="9"/>
+      <c r="AC123" s="9"/>
+      <c r="AD123" s="9"/>
+      <c r="AE123" s="9"/>
+      <c r="AF123" s="9"/>
+      <c r="AG123" s="9"/>
+      <c r="AH123" s="9"/>
+      <c r="AI123" s="9"/>
+      <c r="AJ123" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK123" s="9"/>
+      <c r="AL123" s="9"/>
+      <c r="AM123" s="9"/>
+      <c r="AN123" s="9"/>
+      <c r="AO123" s="9"/>
+      <c r="AP123" s="9"/>
+      <c r="AQ123" s="9"/>
+      <c r="AR123" s="9"/>
+      <c r="AS123" s="9"/>
+      <c r="AT123" s="9"/>
+      <c r="AU123" s="9"/>
+      <c r="AV123" s="9"/>
+      <c r="AW123" s="44"/>
+      <c r="AX123" s="44"/>
+      <c r="AY123" s="44"/>
+      <c r="AZ123" s="44"/>
+      <c r="BA123" s="44"/>
+      <c r="BB123" s="44"/>
+      <c r="BC123" s="44"/>
+    </row>
+    <row r="124" spans="1:55" s="43" customFormat="1">
+      <c r="A124" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9"/>
+      <c r="G124" s="9"/>
+      <c r="H124" s="9"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="9"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
+      <c r="M124" s="9"/>
+      <c r="N124" s="9"/>
+      <c r="O124" s="9"/>
+      <c r="P124" s="9"/>
+      <c r="Q124" s="9"/>
+      <c r="R124" s="9"/>
+      <c r="S124" s="9"/>
+      <c r="T124" s="9"/>
+      <c r="U124" s="9"/>
+      <c r="V124" s="9"/>
+      <c r="W124" s="9"/>
+      <c r="X124" s="9"/>
+      <c r="Y124" s="9"/>
+      <c r="Z124" s="9"/>
+      <c r="AA124" s="9"/>
+      <c r="AB124" s="9"/>
+      <c r="AC124" s="9"/>
+      <c r="AD124" s="9"/>
+      <c r="AE124" s="9"/>
+      <c r="AF124" s="9"/>
+      <c r="AG124" s="9"/>
+      <c r="AH124" s="9"/>
+      <c r="AI124" s="9"/>
+      <c r="AJ124" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK124" s="9"/>
+      <c r="AL124" s="9"/>
+      <c r="AM124" s="9"/>
+      <c r="AN124" s="9"/>
+      <c r="AO124" s="9"/>
+      <c r="AP124" s="9"/>
+      <c r="AQ124" s="9"/>
+      <c r="AR124" s="9"/>
+      <c r="AS124" s="9"/>
+      <c r="AT124" s="9"/>
+      <c r="AU124" s="9"/>
+      <c r="AV124" s="9"/>
+      <c r="AW124" s="44"/>
+      <c r="AX124" s="44"/>
+      <c r="AY124" s="44"/>
+      <c r="AZ124" s="44"/>
+      <c r="BA124" s="44"/>
+      <c r="BB124" s="44"/>
+      <c r="BC124" s="44"/>
+    </row>
+    <row r="125" spans="1:55" s="43" customFormat="1">
+      <c r="A125" s="14"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="9"/>
+      <c r="F125" s="9"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="9"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="9"/>
+      <c r="K125" s="9"/>
+      <c r="L125" s="9"/>
+      <c r="M125" s="9"/>
+      <c r="N125" s="9"/>
+      <c r="O125" s="9"/>
+      <c r="P125" s="9"/>
+      <c r="Q125" s="9"/>
+      <c r="R125" s="9"/>
+      <c r="S125" s="9"/>
+      <c r="T125" s="9"/>
+      <c r="U125" s="9"/>
+      <c r="V125" s="9"/>
+      <c r="W125" s="9"/>
+      <c r="X125" s="9"/>
+      <c r="Y125" s="9"/>
+      <c r="Z125" s="9"/>
+      <c r="AA125" s="9"/>
+      <c r="AB125" s="9"/>
+      <c r="AC125" s="9"/>
+      <c r="AD125" s="9"/>
+      <c r="AE125" s="9"/>
+      <c r="AF125" s="9"/>
+      <c r="AG125" s="9"/>
+      <c r="AH125" s="9"/>
+      <c r="AI125" s="9"/>
+      <c r="AJ125" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="BC117" s="13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="118" spans="1:55">
-      <c r="A118" s="14"/>
-      <c r="AB118" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="BC118" s="13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="119" spans="1:55">
-      <c r="A119" s="13" t="s">
+      <c r="AK125" s="9"/>
+      <c r="AL125" s="9"/>
+      <c r="AM125" s="9"/>
+      <c r="AN125" s="9"/>
+      <c r="AO125" s="9"/>
+      <c r="AP125" s="9"/>
+      <c r="AQ125" s="9"/>
+      <c r="AR125" s="9"/>
+      <c r="AS125" s="9"/>
+      <c r="AT125" s="9"/>
+      <c r="AU125" s="9"/>
+      <c r="AV125" s="9"/>
+      <c r="AW125" s="44"/>
+      <c r="AX125" s="44"/>
+      <c r="AY125" s="44"/>
+      <c r="AZ125" s="44"/>
+      <c r="BA125" s="44"/>
+      <c r="BB125" s="44"/>
+      <c r="BC125" s="44"/>
+    </row>
+    <row r="126" spans="1:55" s="43" customFormat="1">
+      <c r="A126" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="9"/>
+      <c r="F126" s="9"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="9"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="9"/>
+      <c r="K126" s="9"/>
+      <c r="L126" s="9"/>
+      <c r="M126" s="9"/>
+      <c r="N126" s="9"/>
+      <c r="O126" s="9"/>
+      <c r="P126" s="9"/>
+      <c r="Q126" s="9"/>
+      <c r="R126" s="9"/>
+      <c r="S126" s="9"/>
+      <c r="T126" s="9"/>
+      <c r="U126" s="9"/>
+      <c r="V126" s="9"/>
+      <c r="W126" s="9"/>
+      <c r="X126" s="9"/>
+      <c r="Y126" s="9"/>
+      <c r="Z126" s="9"/>
+      <c r="AA126" s="9"/>
+      <c r="AB126" s="9"/>
+      <c r="AC126" s="9"/>
+      <c r="AD126" s="9"/>
+      <c r="AE126" s="9"/>
+      <c r="AF126" s="9"/>
+      <c r="AG126" s="9"/>
+      <c r="AH126" s="9"/>
+      <c r="AI126" s="9"/>
+      <c r="AJ126" s="9"/>
+      <c r="AK126" s="9"/>
+      <c r="AL126" s="9"/>
+      <c r="AM126" s="9"/>
+      <c r="AN126" s="9"/>
+      <c r="AO126" s="9"/>
+      <c r="AP126" s="9"/>
+      <c r="AQ126" s="9"/>
+      <c r="AR126" s="9"/>
+      <c r="AS126" s="9"/>
+      <c r="AT126" s="9"/>
+      <c r="AU126" s="9"/>
+      <c r="AV126" s="9"/>
+      <c r="AW126" s="44"/>
+      <c r="AX126" s="44"/>
+      <c r="AY126" s="44"/>
+      <c r="AZ126" s="44"/>
+      <c r="BA126" s="44"/>
+      <c r="BB126" s="44"/>
+      <c r="BC126" s="44"/>
+    </row>
+    <row r="127" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A127" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9"/>
+      <c r="G127" s="9"/>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="9"/>
+      <c r="M127" s="9"/>
+      <c r="N127" s="9"/>
+      <c r="O127" s="9"/>
+      <c r="P127" s="9"/>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="9"/>
+      <c r="T127" s="9"/>
+      <c r="U127" s="9"/>
+      <c r="V127" s="9"/>
+      <c r="W127" s="9"/>
+      <c r="X127" s="9"/>
+      <c r="Y127" s="9"/>
+      <c r="Z127" s="9"/>
+      <c r="AA127" s="9"/>
+      <c r="AB127" s="9"/>
+      <c r="AC127" s="9"/>
+      <c r="AD127" s="9"/>
+      <c r="AE127" s="9"/>
+      <c r="AF127" s="9"/>
+      <c r="AG127" s="9"/>
+      <c r="AH127" s="9"/>
+      <c r="AI127" s="9"/>
+      <c r="AJ127" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="AK127" s="9"/>
+      <c r="AL127" s="9"/>
+      <c r="AM127" s="9"/>
+      <c r="AN127" s="9"/>
+      <c r="AO127" s="9"/>
+      <c r="AP127" s="9"/>
+      <c r="AQ127" s="9"/>
+      <c r="AR127" s="9"/>
+      <c r="AS127" s="9"/>
+      <c r="AT127" s="9"/>
+      <c r="AU127" s="9"/>
+      <c r="AV127" s="9"/>
+      <c r="AW127" s="44"/>
+      <c r="AX127" s="44"/>
+      <c r="AY127" s="44"/>
+      <c r="AZ127" s="44"/>
+      <c r="BA127" s="44"/>
+      <c r="BB127" s="44"/>
+      <c r="BC127" s="44"/>
+    </row>
+    <row r="128" spans="1:55" s="43" customFormat="1" ht="15">
+      <c r="A128" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
+      <c r="E128" s="9"/>
+      <c r="F128" s="9"/>
+      <c r="G128" s="9"/>
+      <c r="H128" s="9"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="9"/>
+      <c r="K128" s="9"/>
+      <c r="L128" s="9"/>
+      <c r="M128" s="9"/>
+      <c r="N128" s="9"/>
+      <c r="O128" s="9"/>
+      <c r="P128" s="9"/>
+      <c r="Q128" s="9"/>
+      <c r="R128" s="9"/>
+      <c r="S128" s="9"/>
+      <c r="T128" s="9"/>
+      <c r="U128" s="9"/>
+      <c r="V128" s="9"/>
+      <c r="W128" s="9"/>
+      <c r="X128" s="9"/>
+      <c r="Y128" s="9"/>
+      <c r="Z128" s="9"/>
+      <c r="AA128" s="9"/>
+      <c r="AB128" s="9"/>
+      <c r="AC128" s="9"/>
+      <c r="AD128" s="9"/>
+      <c r="AE128" s="9"/>
+      <c r="AF128" s="9"/>
+      <c r="AG128" s="9"/>
+      <c r="AH128" s="9"/>
+      <c r="AI128" s="9"/>
+      <c r="AJ128" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="AK128" s="9"/>
+      <c r="AL128" s="9"/>
+      <c r="AM128" s="9"/>
+      <c r="AN128" s="9"/>
+      <c r="AO128" s="9"/>
+      <c r="AP128" s="9"/>
+      <c r="AQ128" s="9"/>
+      <c r="AR128" s="9"/>
+      <c r="AS128" s="9"/>
+      <c r="AT128" s="9"/>
+      <c r="AU128" s="9"/>
+      <c r="AV128" s="9"/>
+      <c r="AW128" s="44"/>
+      <c r="AX128" s="44"/>
+      <c r="AY128" s="44"/>
+      <c r="AZ128" s="44"/>
+      <c r="BA128" s="44"/>
+      <c r="BB128" s="44"/>
+      <c r="BC128" s="44"/>
+    </row>
+    <row r="129" spans="1:55" s="43" customFormat="1">
+      <c r="A129" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="9"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="9"/>
+      <c r="L129" s="9"/>
+      <c r="M129" s="9"/>
+      <c r="N129" s="9"/>
+      <c r="O129" s="9"/>
+      <c r="P129" s="9"/>
+      <c r="Q129" s="9"/>
+      <c r="R129" s="9"/>
+      <c r="S129" s="9"/>
+      <c r="T129" s="9"/>
+      <c r="U129" s="9"/>
+      <c r="V129" s="9"/>
+      <c r="W129" s="9"/>
+      <c r="X129" s="9"/>
+      <c r="Y129" s="9"/>
+      <c r="Z129" s="9"/>
+      <c r="AA129" s="9"/>
+      <c r="AB129" s="9"/>
+      <c r="AC129" s="9"/>
+      <c r="AD129" s="9"/>
+      <c r="AE129" s="9"/>
+      <c r="AF129" s="9"/>
+      <c r="AG129" s="9"/>
+      <c r="AH129" s="9"/>
+      <c r="AI129" s="9"/>
+      <c r="AJ129" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="AK129" s="9"/>
+      <c r="AL129" s="9"/>
+      <c r="AM129" s="9"/>
+      <c r="AN129" s="9"/>
+      <c r="AO129" s="9"/>
+      <c r="AP129" s="9"/>
+      <c r="AQ129" s="9"/>
+      <c r="AR129" s="9"/>
+      <c r="AS129" s="9"/>
+      <c r="AT129" s="9"/>
+      <c r="AU129" s="9"/>
+      <c r="AV129" s="9"/>
+      <c r="AW129" s="44"/>
+      <c r="AX129" s="44"/>
+      <c r="AY129" s="44"/>
+      <c r="AZ129" s="44"/>
+      <c r="BA129" s="44"/>
+      <c r="BB129" s="44"/>
+      <c r="BC129" s="44"/>
+    </row>
+    <row r="130" spans="1:55" s="43" customFormat="1">
+      <c r="A130" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="9"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="9"/>
+      <c r="K130" s="9"/>
+      <c r="L130" s="9"/>
+      <c r="M130" s="9"/>
+      <c r="N130" s="9"/>
+      <c r="O130" s="9"/>
+      <c r="P130" s="9"/>
+      <c r="Q130" s="9"/>
+      <c r="R130" s="9"/>
+      <c r="S130" s="9"/>
+      <c r="T130" s="9"/>
+      <c r="U130" s="9"/>
+      <c r="V130" s="9"/>
+      <c r="W130" s="9"/>
+      <c r="X130" s="9"/>
+      <c r="Y130" s="9"/>
+      <c r="Z130" s="9"/>
+      <c r="AA130" s="9"/>
+      <c r="AB130" s="9"/>
+      <c r="AC130" s="9"/>
+      <c r="AD130" s="9"/>
+      <c r="AE130" s="9"/>
+      <c r="AF130" s="9"/>
+      <c r="AG130" s="9"/>
+      <c r="AH130" s="9"/>
+      <c r="AI130" s="9"/>
+      <c r="AJ130" s="9"/>
+      <c r="AK130" s="9"/>
+      <c r="AL130" s="9"/>
+      <c r="AM130" s="9"/>
+      <c r="AN130" s="9"/>
+      <c r="AO130" s="9"/>
+      <c r="AP130" s="9"/>
+      <c r="AQ130" s="9"/>
+      <c r="AR130" s="9"/>
+      <c r="AS130" s="9"/>
+      <c r="AT130" s="9"/>
+      <c r="AU130" s="9"/>
+      <c r="AV130" s="9"/>
+      <c r="AW130" s="44"/>
+      <c r="AX130" s="44"/>
+      <c r="AY130" s="44"/>
+      <c r="AZ130" s="44"/>
+      <c r="BA130" s="44"/>
+      <c r="BB130" s="44"/>
+      <c r="BC130" s="44"/>
+    </row>
+    <row r="131" spans="1:55" s="43" customFormat="1">
+      <c r="A131" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="9"/>
+      <c r="K131" s="9"/>
+      <c r="L131" s="9"/>
+      <c r="M131" s="9"/>
+      <c r="N131" s="9"/>
+      <c r="O131" s="9"/>
+      <c r="P131" s="9"/>
+      <c r="Q131" s="9"/>
+      <c r="R131" s="9"/>
+      <c r="S131" s="9"/>
+      <c r="T131" s="9"/>
+      <c r="U131" s="9"/>
+      <c r="V131" s="9"/>
+      <c r="W131" s="9"/>
+      <c r="X131" s="9"/>
+      <c r="Y131" s="9"/>
+      <c r="Z131" s="9"/>
+      <c r="AA131" s="9"/>
+      <c r="AB131" s="9"/>
+      <c r="AC131" s="9"/>
+      <c r="AD131" s="9"/>
+      <c r="AE131" s="9"/>
+      <c r="AF131" s="9"/>
+      <c r="AG131" s="9"/>
+      <c r="AH131" s="9"/>
+      <c r="AI131" s="9"/>
+      <c r="AJ131" s="9"/>
+      <c r="AK131" s="9"/>
+      <c r="AL131" s="9"/>
+      <c r="AM131" s="9"/>
+      <c r="AN131" s="9"/>
+      <c r="AO131" s="9"/>
+      <c r="AP131" s="9"/>
+      <c r="AQ131" s="9"/>
+      <c r="AR131" s="9"/>
+      <c r="AS131" s="9"/>
+      <c r="AT131" s="9"/>
+      <c r="AU131" s="9"/>
+      <c r="AV131" s="9"/>
+      <c r="AW131" s="44"/>
+      <c r="AX131" s="44"/>
+      <c r="AY131" s="44"/>
+      <c r="AZ131" s="44"/>
+      <c r="BA131" s="44"/>
+      <c r="BB131" s="44"/>
+      <c r="BC131" s="44"/>
+    </row>
+    <row r="132" spans="1:55" s="43" customFormat="1">
+      <c r="A132" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
+      <c r="E132" s="9"/>
+      <c r="F132" s="9"/>
+      <c r="G132" s="9"/>
+      <c r="H132" s="9"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="9"/>
+      <c r="K132" s="9"/>
+      <c r="L132" s="9"/>
+      <c r="M132" s="9"/>
+      <c r="N132" s="9"/>
+      <c r="O132" s="9"/>
+      <c r="P132" s="9"/>
+      <c r="Q132" s="9"/>
+      <c r="R132" s="9"/>
+      <c r="S132" s="9"/>
+      <c r="T132" s="9"/>
+      <c r="U132" s="9"/>
+      <c r="V132" s="9"/>
+      <c r="W132" s="9"/>
+      <c r="X132" s="9"/>
+      <c r="Y132" s="9"/>
+      <c r="Z132" s="9"/>
+      <c r="AA132" s="9"/>
+      <c r="AB132" s="9"/>
+      <c r="AC132" s="9"/>
+      <c r="AD132" s="9"/>
+      <c r="AE132" s="9"/>
+      <c r="AF132" s="9"/>
+      <c r="AG132" s="9"/>
+      <c r="AH132" s="9"/>
+      <c r="AI132" s="9"/>
+      <c r="AJ132" s="9"/>
+      <c r="AK132" s="9"/>
+      <c r="AL132" s="9"/>
+      <c r="AM132" s="9"/>
+      <c r="AN132" s="9"/>
+      <c r="AO132" s="9"/>
+      <c r="AP132" s="9"/>
+      <c r="AQ132" s="9"/>
+      <c r="AR132" s="9"/>
+      <c r="AS132" s="9"/>
+      <c r="AT132" s="9"/>
+      <c r="AU132" s="9"/>
+      <c r="AV132" s="9"/>
+      <c r="AW132" s="44"/>
+      <c r="AX132" s="44"/>
+      <c r="AY132" s="44"/>
+      <c r="AZ132" s="44"/>
+      <c r="BA132" s="44"/>
+      <c r="BB132" s="44"/>
+      <c r="BC132" s="44"/>
+    </row>
+    <row r="133" spans="1:55" s="43" customFormat="1">
+      <c r="A133" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
+      <c r="E133" s="9"/>
+      <c r="F133" s="9"/>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="9"/>
+      <c r="K133" s="9"/>
+      <c r="L133" s="9"/>
+      <c r="M133" s="9"/>
+      <c r="N133" s="9"/>
+      <c r="O133" s="9"/>
+      <c r="P133" s="9"/>
+      <c r="Q133" s="9"/>
+      <c r="R133" s="9"/>
+      <c r="S133" s="9"/>
+      <c r="T133" s="9"/>
+      <c r="U133" s="9"/>
+      <c r="V133" s="9"/>
+      <c r="W133" s="9"/>
+      <c r="X133" s="9"/>
+      <c r="Y133" s="9"/>
+      <c r="Z133" s="9"/>
+      <c r="AA133" s="9"/>
+      <c r="AB133" s="9"/>
+      <c r="AC133" s="9"/>
+      <c r="AD133" s="9"/>
+      <c r="AE133" s="9"/>
+      <c r="AF133" s="9"/>
+      <c r="AG133" s="9"/>
+      <c r="AH133" s="9"/>
+      <c r="AI133" s="9"/>
+      <c r="AJ133" s="9"/>
+      <c r="AK133" s="9"/>
+      <c r="AL133" s="9"/>
+      <c r="AM133" s="9"/>
+      <c r="AN133" s="9"/>
+      <c r="AO133" s="9"/>
+      <c r="AP133" s="9"/>
+      <c r="AQ133" s="9"/>
+      <c r="AR133" s="9"/>
+      <c r="AS133" s="9"/>
+      <c r="AT133" s="9"/>
+      <c r="AU133" s="9"/>
+      <c r="AV133" s="9"/>
+      <c r="AW133" s="44"/>
+      <c r="AX133" s="44"/>
+      <c r="AY133" s="44"/>
+      <c r="AZ133" s="44"/>
+      <c r="BA133" s="44"/>
+      <c r="BB133" s="44"/>
+      <c r="BC133" s="44"/>
+    </row>
+    <row r="134" spans="1:55" s="43" customFormat="1">
+      <c r="A134" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="9"/>
+      <c r="F134" s="9"/>
+      <c r="G134" s="9"/>
+      <c r="H134" s="9"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="9"/>
+      <c r="K134" s="9"/>
+      <c r="L134" s="9"/>
+      <c r="M134" s="9"/>
+      <c r="N134" s="9"/>
+      <c r="O134" s="9"/>
+      <c r="P134" s="9"/>
+      <c r="Q134" s="9"/>
+      <c r="R134" s="9"/>
+      <c r="S134" s="9"/>
+      <c r="T134" s="9"/>
+      <c r="U134" s="9"/>
+      <c r="V134" s="9"/>
+      <c r="W134" s="9"/>
+      <c r="X134" s="9"/>
+      <c r="Y134" s="9"/>
+      <c r="Z134" s="9"/>
+      <c r="AA134" s="9"/>
+      <c r="AB134" s="9"/>
+      <c r="AC134" s="9"/>
+      <c r="AD134" s="9"/>
+      <c r="AE134" s="9"/>
+      <c r="AF134" s="9"/>
+      <c r="AG134" s="9"/>
+      <c r="AH134" s="9"/>
+      <c r="AI134" s="9"/>
+      <c r="AJ134" s="9"/>
+      <c r="AK134" s="9"/>
+      <c r="AL134" s="9"/>
+      <c r="AM134" s="9"/>
+      <c r="AN134" s="9"/>
+      <c r="AO134" s="9"/>
+      <c r="AP134" s="9"/>
+      <c r="AQ134" s="9"/>
+      <c r="AR134" s="9"/>
+      <c r="AS134" s="9"/>
+      <c r="AT134" s="9"/>
+      <c r="AU134" s="9"/>
+      <c r="AV134" s="9"/>
+      <c r="AW134" s="44"/>
+      <c r="AX134" s="44"/>
+      <c r="AY134" s="44"/>
+      <c r="AZ134" s="44"/>
+      <c r="BA134" s="44"/>
+      <c r="BB134" s="44"/>
+      <c r="BC134" s="44"/>
+    </row>
+    <row r="135" spans="1:55" s="43" customFormat="1">
+      <c r="A135" s="14"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
+      <c r="E135" s="9"/>
+      <c r="F135" s="9"/>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="9"/>
+      <c r="K135" s="9"/>
+      <c r="L135" s="9"/>
+      <c r="M135" s="9"/>
+      <c r="N135" s="9"/>
+      <c r="O135" s="9"/>
+      <c r="P135" s="9"/>
+      <c r="Q135" s="9"/>
+      <c r="R135" s="9"/>
+      <c r="S135" s="9"/>
+      <c r="T135" s="9"/>
+      <c r="U135" s="9"/>
+      <c r="V135" s="9"/>
+      <c r="W135" s="9"/>
+      <c r="X135" s="9"/>
+      <c r="Y135" s="9"/>
+      <c r="Z135" s="9"/>
+      <c r="AA135" s="9"/>
+      <c r="AB135" s="9"/>
+      <c r="AC135" s="9"/>
+      <c r="AD135" s="9"/>
+      <c r="AE135" s="9"/>
+      <c r="AF135" s="9"/>
+      <c r="AG135" s="9"/>
+      <c r="AH135" s="9"/>
+      <c r="AI135" s="9"/>
+      <c r="AJ135" s="9"/>
+      <c r="AK135" s="9"/>
+      <c r="AL135" s="9"/>
+      <c r="AM135" s="9"/>
+      <c r="AN135" s="9"/>
+      <c r="AO135" s="9"/>
+      <c r="AP135" s="9"/>
+      <c r="AQ135" s="9"/>
+      <c r="AR135" s="9"/>
+      <c r="AS135" s="9"/>
+      <c r="AT135" s="9"/>
+      <c r="AU135" s="9"/>
+      <c r="AV135" s="9"/>
+      <c r="AW135" s="44"/>
+      <c r="AX135" s="44"/>
+      <c r="AY135" s="44"/>
+      <c r="AZ135" s="44"/>
+      <c r="BA135" s="44"/>
+      <c r="BB135" s="44"/>
+      <c r="BC135" s="44"/>
+    </row>
+    <row r="136" spans="1:55" s="43" customFormat="1">
+      <c r="A136" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
+      <c r="E136" s="9"/>
+      <c r="F136" s="9"/>
+      <c r="G136" s="9"/>
+      <c r="H136" s="9"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="9"/>
+      <c r="K136" s="9"/>
+      <c r="L136" s="9"/>
+      <c r="M136" s="9"/>
+      <c r="N136" s="9"/>
+      <c r="O136" s="9"/>
+      <c r="P136" s="9"/>
+      <c r="Q136" s="9"/>
+      <c r="R136" s="9"/>
+      <c r="S136" s="9"/>
+      <c r="T136" s="9"/>
+      <c r="U136" s="9"/>
+      <c r="V136" s="9"/>
+      <c r="W136" s="9"/>
+      <c r="X136" s="9"/>
+      <c r="Y136" s="9"/>
+      <c r="Z136" s="9"/>
+      <c r="AA136" s="9"/>
+      <c r="AB136" s="9"/>
+      <c r="AC136" s="9"/>
+      <c r="AD136" s="9"/>
+      <c r="AE136" s="9"/>
+      <c r="AF136" s="9"/>
+      <c r="AG136" s="9"/>
+      <c r="AH136" s="9"/>
+      <c r="AI136" s="9"/>
+      <c r="AJ136" s="9"/>
+      <c r="AK136" s="9"/>
+      <c r="AL136" s="9"/>
+      <c r="AM136" s="9"/>
+      <c r="AN136" s="9"/>
+      <c r="AO136" s="9"/>
+      <c r="AP136" s="9"/>
+      <c r="AQ136" s="9"/>
+      <c r="AR136" s="9"/>
+      <c r="AS136" s="9"/>
+      <c r="AT136" s="9"/>
+      <c r="AU136" s="9"/>
+      <c r="AV136" s="9"/>
+      <c r="AW136" s="44"/>
+      <c r="AX136" s="44"/>
+      <c r="AY136" s="44"/>
+      <c r="AZ136" s="44"/>
+      <c r="BA136" s="44"/>
+      <c r="BB136" s="44"/>
+      <c r="BC136" s="44"/>
+    </row>
+    <row r="137" spans="1:55" s="43" customFormat="1">
+      <c r="A137" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="9"/>
+      <c r="H137" s="9"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="9"/>
+      <c r="K137" s="9"/>
+      <c r="L137" s="9"/>
+      <c r="M137" s="9"/>
+      <c r="N137" s="9"/>
+      <c r="O137" s="9"/>
+      <c r="P137" s="9"/>
+      <c r="Q137" s="9"/>
+      <c r="R137" s="9"/>
+      <c r="S137" s="9"/>
+      <c r="T137" s="9"/>
+      <c r="U137" s="9"/>
+      <c r="V137" s="9"/>
+      <c r="W137" s="9"/>
+      <c r="X137" s="9"/>
+      <c r="Y137" s="9"/>
+      <c r="Z137" s="9"/>
+      <c r="AA137" s="9"/>
+      <c r="AB137" s="9"/>
+      <c r="AC137" s="9"/>
+      <c r="AD137" s="9"/>
+      <c r="AE137" s="9"/>
+      <c r="AF137" s="9"/>
+      <c r="AG137" s="9"/>
+      <c r="AH137" s="9"/>
+      <c r="AI137" s="9"/>
+      <c r="AJ137" s="9"/>
+      <c r="AK137" s="9"/>
+      <c r="AL137" s="9"/>
+      <c r="AM137" s="9"/>
+      <c r="AN137" s="9"/>
+      <c r="AO137" s="9"/>
+      <c r="AP137" s="9"/>
+      <c r="AQ137" s="9"/>
+      <c r="AR137" s="9"/>
+      <c r="AS137" s="9"/>
+      <c r="AT137" s="9"/>
+      <c r="AU137" s="9"/>
+      <c r="AV137" s="9"/>
+      <c r="AW137" s="44"/>
+      <c r="AX137" s="44"/>
+      <c r="AY137" s="44"/>
+      <c r="AZ137" s="44"/>
+      <c r="BA137" s="44"/>
+      <c r="BB137" s="44"/>
+      <c r="BC137" s="44"/>
+    </row>
+    <row r="138" spans="1:55" s="43" customFormat="1">
+      <c r="A138" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
+      <c r="E138" s="9"/>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9"/>
+      <c r="H138" s="9"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="9"/>
+      <c r="K138" s="9"/>
+      <c r="L138" s="9"/>
+      <c r="M138" s="9"/>
+      <c r="N138" s="9"/>
+      <c r="O138" s="9"/>
+      <c r="P138" s="9"/>
+      <c r="Q138" s="9"/>
+      <c r="R138" s="9"/>
+      <c r="S138" s="9"/>
+      <c r="T138" s="9"/>
+      <c r="U138" s="9"/>
+      <c r="V138" s="9"/>
+      <c r="W138" s="9"/>
+      <c r="X138" s="9"/>
+      <c r="Y138" s="9"/>
+      <c r="Z138" s="9"/>
+      <c r="AA138" s="9"/>
+      <c r="AB138" s="9"/>
+      <c r="AC138" s="9"/>
+      <c r="AD138" s="9"/>
+      <c r="AE138" s="9"/>
+      <c r="AF138" s="9"/>
+      <c r="AG138" s="9"/>
+      <c r="AH138" s="9"/>
+      <c r="AI138" s="9"/>
+      <c r="AJ138" s="9"/>
+      <c r="AK138" s="9"/>
+      <c r="AL138" s="9"/>
+      <c r="AM138" s="9"/>
+      <c r="AN138" s="9"/>
+      <c r="AO138" s="9"/>
+      <c r="AP138" s="9"/>
+      <c r="AQ138" s="9"/>
+      <c r="AR138" s="9"/>
+      <c r="AS138" s="9"/>
+      <c r="AT138" s="9"/>
+      <c r="AU138" s="9"/>
+      <c r="AV138" s="9"/>
+      <c r="AW138" s="44"/>
+      <c r="AX138" s="44"/>
+      <c r="AY138" s="44"/>
+      <c r="AZ138" s="44"/>
+      <c r="BA138" s="44"/>
+      <c r="BB138" s="44"/>
+      <c r="BC138" s="44"/>
+    </row>
+    <row r="139" spans="1:55" s="43" customFormat="1">
+      <c r="A139" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
+      <c r="E139" s="9"/>
+      <c r="F139" s="9"/>
+      <c r="G139" s="9"/>
+      <c r="H139" s="9"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="9"/>
+      <c r="K139" s="9"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+      <c r="N139" s="9"/>
+      <c r="O139" s="9"/>
+      <c r="P139" s="9"/>
+      <c r="Q139" s="9"/>
+      <c r="R139" s="9"/>
+      <c r="S139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
+      <c r="V139" s="9"/>
+      <c r="W139" s="9"/>
+      <c r="X139" s="9"/>
+      <c r="Y139" s="9"/>
+      <c r="Z139" s="9"/>
+      <c r="AA139" s="9"/>
+      <c r="AB139" s="9"/>
+      <c r="AC139" s="9"/>
+      <c r="AD139" s="9"/>
+      <c r="AE139" s="9"/>
+      <c r="AF139" s="9"/>
+      <c r="AG139" s="9"/>
+      <c r="AH139" s="9"/>
+      <c r="AI139" s="9"/>
+      <c r="AJ139" s="9"/>
+      <c r="AK139" s="9"/>
+      <c r="AL139" s="9"/>
+      <c r="AM139" s="9"/>
+      <c r="AN139" s="9"/>
+      <c r="AO139" s="9"/>
+      <c r="AP139" s="9"/>
+      <c r="AQ139" s="9"/>
+      <c r="AR139" s="9"/>
+      <c r="AS139" s="9"/>
+      <c r="AT139" s="9"/>
+      <c r="AU139" s="9"/>
+      <c r="AV139" s="9"/>
+      <c r="AW139" s="44"/>
+      <c r="AX139" s="44"/>
+      <c r="AY139" s="44"/>
+      <c r="AZ139" s="44"/>
+      <c r="BA139" s="44"/>
+      <c r="BB139" s="44"/>
+      <c r="BC139" s="44"/>
+    </row>
+    <row r="140" spans="1:55" s="43" customFormat="1">
+      <c r="A140" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9"/>
+      <c r="E140" s="9"/>
+      <c r="F140" s="9"/>
+      <c r="G140" s="9"/>
+      <c r="H140" s="9"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="9"/>
+      <c r="K140" s="9"/>
+      <c r="L140" s="9"/>
+      <c r="M140" s="9"/>
+      <c r="N140" s="9"/>
+      <c r="O140" s="9"/>
+      <c r="P140" s="9"/>
+      <c r="Q140" s="9"/>
+      <c r="R140" s="9"/>
+      <c r="S140" s="9"/>
+      <c r="T140" s="9"/>
+      <c r="U140" s="9"/>
+      <c r="V140" s="9"/>
+      <c r="W140" s="9"/>
+      <c r="X140" s="9"/>
+      <c r="Y140" s="9"/>
+      <c r="Z140" s="9"/>
+      <c r="AA140" s="9"/>
+      <c r="AB140" s="9"/>
+      <c r="AC140" s="9"/>
+      <c r="AD140" s="9"/>
+      <c r="AE140" s="9"/>
+      <c r="AF140" s="9"/>
+      <c r="AG140" s="9"/>
+      <c r="AH140" s="9"/>
+      <c r="AI140" s="9"/>
+      <c r="AJ140" s="9"/>
+      <c r="AK140" s="9"/>
+      <c r="AL140" s="9"/>
+      <c r="AM140" s="9"/>
+      <c r="AN140" s="9"/>
+      <c r="AO140" s="9"/>
+      <c r="AP140" s="9"/>
+      <c r="AQ140" s="9"/>
+      <c r="AR140" s="9"/>
+      <c r="AS140" s="9"/>
+      <c r="AT140" s="9"/>
+      <c r="AU140" s="9"/>
+      <c r="AV140" s="9"/>
+      <c r="AW140" s="44"/>
+      <c r="AX140" s="44"/>
+      <c r="AY140" s="44"/>
+      <c r="AZ140" s="44"/>
+      <c r="BA140" s="44"/>
+      <c r="BB140" s="44"/>
+      <c r="BC140" s="44"/>
+    </row>
+    <row r="141" spans="1:55" s="43" customFormat="1">
+      <c r="A141" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
+      <c r="E141" s="9"/>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="9"/>
+      <c r="K141" s="9"/>
+      <c r="L141" s="9"/>
+      <c r="M141" s="9"/>
+      <c r="N141" s="9"/>
+      <c r="O141" s="9"/>
+      <c r="P141" s="9"/>
+      <c r="Q141" s="9"/>
+      <c r="R141" s="9"/>
+      <c r="S141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
+      <c r="V141" s="9"/>
+      <c r="W141" s="9"/>
+      <c r="X141" s="9"/>
+      <c r="Y141" s="9"/>
+      <c r="Z141" s="9"/>
+      <c r="AA141" s="9"/>
+      <c r="AB141" s="9"/>
+      <c r="AC141" s="9"/>
+      <c r="AD141" s="9"/>
+      <c r="AE141" s="9"/>
+      <c r="AF141" s="9"/>
+      <c r="AG141" s="9"/>
+      <c r="AH141" s="9"/>
+      <c r="AI141" s="9"/>
+      <c r="AJ141" s="9"/>
+      <c r="AK141" s="9"/>
+      <c r="AL141" s="9"/>
+      <c r="AM141" s="9"/>
+      <c r="AN141" s="9"/>
+      <c r="AO141" s="9"/>
+      <c r="AP141" s="9"/>
+      <c r="AQ141" s="9"/>
+      <c r="AR141" s="9"/>
+      <c r="AS141" s="9"/>
+      <c r="AT141" s="9"/>
+      <c r="AU141" s="9"/>
+      <c r="AV141" s="9"/>
+      <c r="AW141" s="44"/>
+      <c r="AX141" s="44"/>
+      <c r="AY141" s="44"/>
+      <c r="AZ141" s="44"/>
+      <c r="BA141" s="44"/>
+      <c r="BB141" s="44"/>
+      <c r="BC141" s="44"/>
+    </row>
+    <row r="142" spans="1:55" s="43" customFormat="1">
+      <c r="A142" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9"/>
+      <c r="E142" s="9"/>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9"/>
+      <c r="H142" s="9"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="9"/>
+      <c r="K142" s="9"/>
+      <c r="L142" s="9"/>
+      <c r="M142" s="9"/>
+      <c r="N142" s="9"/>
+      <c r="O142" s="9"/>
+      <c r="P142" s="9"/>
+      <c r="Q142" s="9"/>
+      <c r="R142" s="9"/>
+      <c r="S142" s="9"/>
+      <c r="T142" s="9"/>
+      <c r="U142" s="9"/>
+      <c r="V142" s="9"/>
+      <c r="W142" s="9"/>
+      <c r="X142" s="9"/>
+      <c r="Y142" s="9"/>
+      <c r="Z142" s="9"/>
+      <c r="AA142" s="9"/>
+      <c r="AB142" s="9"/>
+      <c r="AC142" s="9"/>
+      <c r="AD142" s="9"/>
+      <c r="AE142" s="9"/>
+      <c r="AF142" s="9"/>
+      <c r="AG142" s="9"/>
+      <c r="AH142" s="9"/>
+      <c r="AI142" s="9"/>
+      <c r="AJ142" s="9"/>
+      <c r="AK142" s="9"/>
+      <c r="AL142" s="9"/>
+      <c r="AM142" s="9"/>
+      <c r="AN142" s="9"/>
+      <c r="AO142" s="9"/>
+      <c r="AP142" s="9"/>
+      <c r="AQ142" s="9"/>
+      <c r="AR142" s="9"/>
+      <c r="AS142" s="9"/>
+      <c r="AT142" s="9"/>
+      <c r="AU142" s="9"/>
+      <c r="AV142" s="9"/>
+      <c r="AW142" s="44"/>
+      <c r="AX142" s="44"/>
+      <c r="AY142" s="44"/>
+      <c r="AZ142" s="44"/>
+      <c r="BA142" s="44"/>
+      <c r="BB142" s="44"/>
+      <c r="BC142" s="44"/>
+    </row>
+    <row r="143" spans="1:55" s="43" customFormat="1">
+      <c r="A143" s="14"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
+      <c r="E143" s="9"/>
+      <c r="F143" s="9"/>
+      <c r="G143" s="9"/>
+      <c r="H143" s="9"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="9"/>
+      <c r="K143" s="9"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="9"/>
+      <c r="O143" s="9"/>
+      <c r="P143" s="9"/>
+      <c r="Q143" s="9"/>
+      <c r="R143" s="9"/>
+      <c r="S143" s="9"/>
+      <c r="T143" s="9"/>
+      <c r="U143" s="9"/>
+      <c r="V143" s="9"/>
+      <c r="W143" s="9"/>
+      <c r="X143" s="9"/>
+      <c r="Y143" s="9"/>
+      <c r="Z143" s="9"/>
+      <c r="AA143" s="9"/>
+      <c r="AB143" s="9"/>
+      <c r="AC143" s="9"/>
+      <c r="AD143" s="9"/>
+      <c r="AE143" s="9"/>
+      <c r="AF143" s="9"/>
+      <c r="AG143" s="9"/>
+      <c r="AH143" s="9"/>
+      <c r="AI143" s="9"/>
+      <c r="AJ143" s="9"/>
+      <c r="AK143" s="9"/>
+      <c r="AL143" s="9"/>
+      <c r="AM143" s="9"/>
+      <c r="AN143" s="9"/>
+      <c r="AO143" s="9"/>
+      <c r="AP143" s="9"/>
+      <c r="AQ143" s="9"/>
+      <c r="AR143" s="9"/>
+      <c r="AS143" s="9"/>
+      <c r="AT143" s="9"/>
+      <c r="AU143" s="9"/>
+      <c r="AV143" s="9"/>
+      <c r="AW143" s="44"/>
+      <c r="AX143" s="44"/>
+      <c r="AY143" s="44"/>
+      <c r="AZ143" s="44"/>
+      <c r="BA143" s="44"/>
+      <c r="BB143" s="44"/>
+      <c r="BC143" s="44"/>
+    </row>
+    <row r="144" spans="1:55" s="43" customFormat="1">
+      <c r="A144" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
+      <c r="D144" s="9"/>
+      <c r="E144" s="9"/>
+      <c r="F144" s="9"/>
+      <c r="G144" s="9"/>
+      <c r="H144" s="9"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="9"/>
+      <c r="K144" s="9"/>
+      <c r="L144" s="9"/>
+      <c r="M144" s="9"/>
+      <c r="N144" s="9"/>
+      <c r="O144" s="9"/>
+      <c r="P144" s="9"/>
+      <c r="Q144" s="9"/>
+      <c r="R144" s="9"/>
+      <c r="S144" s="9"/>
+      <c r="T144" s="9"/>
+      <c r="U144" s="9"/>
+      <c r="V144" s="9"/>
+      <c r="W144" s="9"/>
+      <c r="X144" s="9"/>
+      <c r="Y144" s="9"/>
+      <c r="Z144" s="9"/>
+      <c r="AA144" s="9"/>
+      <c r="AB144" s="9"/>
+      <c r="AC144" s="9"/>
+      <c r="AD144" s="9"/>
+      <c r="AE144" s="9"/>
+      <c r="AF144" s="9"/>
+      <c r="AG144" s="9"/>
+      <c r="AH144" s="9"/>
+      <c r="AI144" s="9"/>
+      <c r="AJ144" s="9"/>
+      <c r="AK144" s="9"/>
+      <c r="AL144" s="9"/>
+      <c r="AM144" s="9"/>
+      <c r="AN144" s="9"/>
+      <c r="AO144" s="9"/>
+      <c r="AP144" s="9"/>
+      <c r="AQ144" s="9"/>
+      <c r="AR144" s="9"/>
+      <c r="AS144" s="9"/>
+      <c r="AT144" s="9"/>
+      <c r="AU144" s="9"/>
+      <c r="AV144" s="9"/>
+      <c r="AW144" s="44"/>
+      <c r="AX144" s="44"/>
+      <c r="AY144" s="44"/>
+      <c r="AZ144" s="44"/>
+      <c r="BA144" s="44"/>
+      <c r="BB144" s="44"/>
+      <c r="BC144" s="44"/>
+    </row>
+    <row r="145" spans="1:79" s="43" customFormat="1">
+      <c r="A145" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AB119" s="14"/>
-      <c r="BC119" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="120" spans="1:55">
-      <c r="A120" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB120" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="BC120" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="121" spans="1:55">
-      <c r="A121" s="13" t="s">
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
+      <c r="E145" s="9"/>
+      <c r="F145" s="9"/>
+      <c r="G145" s="9"/>
+      <c r="H145" s="9"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="9"/>
+      <c r="K145" s="9"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="9"/>
+      <c r="N145" s="9"/>
+      <c r="O145" s="9"/>
+      <c r="P145" s="9"/>
+      <c r="Q145" s="9"/>
+      <c r="R145" s="9"/>
+      <c r="S145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
+      <c r="V145" s="9"/>
+      <c r="W145" s="9"/>
+      <c r="X145" s="9"/>
+      <c r="Y145" s="9"/>
+      <c r="Z145" s="9"/>
+      <c r="AA145" s="9"/>
+      <c r="AB145" s="9"/>
+      <c r="AC145" s="9"/>
+      <c r="AD145" s="9"/>
+      <c r="AE145" s="9"/>
+      <c r="AF145" s="9"/>
+      <c r="AG145" s="9"/>
+      <c r="AH145" s="9"/>
+      <c r="AI145" s="9"/>
+      <c r="AJ145" s="9"/>
+      <c r="AK145" s="9"/>
+      <c r="AL145" s="9"/>
+      <c r="AM145" s="9"/>
+      <c r="AN145" s="9"/>
+      <c r="AO145" s="9"/>
+      <c r="AP145" s="9"/>
+      <c r="AQ145" s="9"/>
+      <c r="AR145" s="9"/>
+      <c r="AS145" s="9"/>
+      <c r="AT145" s="9"/>
+      <c r="AU145" s="9"/>
+      <c r="AV145" s="9"/>
+      <c r="AW145" s="44"/>
+      <c r="AX145" s="44"/>
+      <c r="AY145" s="44"/>
+      <c r="AZ145" s="44"/>
+      <c r="BA145" s="44"/>
+      <c r="BB145" s="44"/>
+      <c r="BC145" s="44"/>
+    </row>
+    <row r="146" spans="1:79" s="43" customFormat="1">
+      <c r="A146" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
+      <c r="D146" s="9"/>
+      <c r="E146" s="9"/>
+      <c r="F146" s="9"/>
+      <c r="G146" s="9"/>
+      <c r="H146" s="9"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="9"/>
+      <c r="K146" s="9"/>
+      <c r="L146" s="9"/>
+      <c r="M146" s="9"/>
+      <c r="N146" s="9"/>
+      <c r="O146" s="9"/>
+      <c r="P146" s="9"/>
+      <c r="Q146" s="9"/>
+      <c r="R146" s="9"/>
+      <c r="S146" s="9"/>
+      <c r="T146" s="9"/>
+      <c r="U146" s="9"/>
+      <c r="V146" s="9"/>
+      <c r="W146" s="9"/>
+      <c r="X146" s="9"/>
+      <c r="Y146" s="9"/>
+      <c r="Z146" s="9"/>
+      <c r="AA146" s="9"/>
+      <c r="AB146" s="9"/>
+      <c r="AC146" s="9"/>
+      <c r="AD146" s="9"/>
+      <c r="AE146" s="9"/>
+      <c r="AF146" s="9"/>
+      <c r="AG146" s="9"/>
+      <c r="AH146" s="9"/>
+      <c r="AI146" s="9"/>
+      <c r="AJ146" s="9"/>
+      <c r="AK146" s="9"/>
+      <c r="AL146" s="9"/>
+      <c r="AM146" s="9"/>
+      <c r="AN146" s="9"/>
+      <c r="AO146" s="9"/>
+      <c r="AP146" s="9"/>
+      <c r="AQ146" s="9"/>
+      <c r="AR146" s="9"/>
+      <c r="AS146" s="9"/>
+      <c r="AT146" s="9"/>
+      <c r="AU146" s="9"/>
+      <c r="AV146" s="9"/>
+      <c r="AW146" s="44"/>
+      <c r="AX146" s="44"/>
+      <c r="AY146" s="44"/>
+      <c r="AZ146" s="44"/>
+      <c r="BA146" s="44"/>
+      <c r="BB146" s="44"/>
+      <c r="BC146" s="44"/>
+    </row>
+    <row r="147" spans="1:79" s="43" customFormat="1">
+      <c r="A147" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9"/>
+      <c r="D147" s="9"/>
+      <c r="E147" s="9"/>
+      <c r="F147" s="9"/>
+      <c r="G147" s="9"/>
+      <c r="H147" s="9"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="9"/>
+      <c r="K147" s="9"/>
+      <c r="L147" s="9"/>
+      <c r="M147" s="9"/>
+      <c r="N147" s="9"/>
+      <c r="O147" s="9"/>
+      <c r="P147" s="9"/>
+      <c r="Q147" s="9"/>
+      <c r="R147" s="9"/>
+      <c r="S147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
+      <c r="V147" s="9"/>
+      <c r="W147" s="9"/>
+      <c r="X147" s="9"/>
+      <c r="Y147" s="9"/>
+      <c r="Z147" s="9"/>
+      <c r="AA147" s="9"/>
+      <c r="AB147" s="9"/>
+      <c r="AC147" s="9"/>
+      <c r="AD147" s="9"/>
+      <c r="AE147" s="9"/>
+      <c r="AF147" s="9"/>
+      <c r="AG147" s="9"/>
+      <c r="AH147" s="9"/>
+      <c r="AI147" s="9"/>
+      <c r="AJ147" s="9"/>
+      <c r="AK147" s="9"/>
+      <c r="AL147" s="9"/>
+      <c r="AM147" s="9"/>
+      <c r="AN147" s="9"/>
+      <c r="AO147" s="9"/>
+      <c r="AP147" s="9"/>
+      <c r="AQ147" s="9"/>
+      <c r="AR147" s="9"/>
+      <c r="AS147" s="9"/>
+      <c r="AT147" s="9"/>
+      <c r="AU147" s="9"/>
+      <c r="AV147" s="9"/>
+      <c r="AW147" s="44"/>
+      <c r="AX147" s="44"/>
+      <c r="AY147" s="44"/>
+      <c r="AZ147" s="44"/>
+      <c r="BA147" s="44"/>
+      <c r="BB147" s="44"/>
+      <c r="BC147" s="44"/>
+    </row>
+    <row r="148" spans="1:79" s="43" customFormat="1">
+      <c r="A148" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9"/>
+      <c r="D148" s="9"/>
+      <c r="E148" s="9"/>
+      <c r="F148" s="9"/>
+      <c r="G148" s="9"/>
+      <c r="H148" s="9"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="9"/>
+      <c r="K148" s="9"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="9"/>
+      <c r="O148" s="9"/>
+      <c r="P148" s="9"/>
+      <c r="Q148" s="9"/>
+      <c r="R148" s="9"/>
+      <c r="S148" s="9"/>
+      <c r="T148" s="9"/>
+      <c r="U148" s="9"/>
+      <c r="V148" s="9"/>
+      <c r="W148" s="9"/>
+      <c r="X148" s="9"/>
+      <c r="Y148" s="9"/>
+      <c r="Z148" s="9"/>
+      <c r="AA148" s="9"/>
+      <c r="AB148" s="9"/>
+      <c r="AC148" s="9"/>
+      <c r="AD148" s="9"/>
+      <c r="AE148" s="9"/>
+      <c r="AF148" s="9"/>
+      <c r="AG148" s="9"/>
+      <c r="AH148" s="9"/>
+      <c r="AI148" s="9"/>
+      <c r="AJ148" s="9"/>
+      <c r="AK148" s="9"/>
+      <c r="AL148" s="9"/>
+      <c r="AM148" s="9"/>
+      <c r="AN148" s="9"/>
+      <c r="AO148" s="9"/>
+      <c r="AP148" s="9"/>
+      <c r="AQ148" s="9"/>
+      <c r="AR148" s="9"/>
+      <c r="AS148" s="9"/>
+      <c r="AT148" s="9"/>
+      <c r="AU148" s="9"/>
+      <c r="AV148" s="9"/>
+      <c r="AW148" s="44"/>
+      <c r="AX148" s="44"/>
+      <c r="AY148" s="44"/>
+      <c r="AZ148" s="44"/>
+      <c r="BA148" s="44"/>
+      <c r="BB148" s="44"/>
+      <c r="BC148" s="44"/>
+    </row>
+    <row r="149" spans="1:79" s="43" customFormat="1">
+      <c r="A149" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="9"/>
+      <c r="E149" s="9"/>
+      <c r="F149" s="9"/>
+      <c r="G149" s="9"/>
+      <c r="H149" s="9"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="9"/>
+      <c r="K149" s="9"/>
+      <c r="L149" s="9"/>
+      <c r="M149" s="9"/>
+      <c r="N149" s="9"/>
+      <c r="O149" s="9"/>
+      <c r="P149" s="9"/>
+      <c r="Q149" s="9"/>
+      <c r="R149" s="9"/>
+      <c r="S149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
+      <c r="V149" s="9"/>
+      <c r="W149" s="9"/>
+      <c r="X149" s="9"/>
+      <c r="Y149" s="9"/>
+      <c r="Z149" s="9"/>
+      <c r="AA149" s="9"/>
+      <c r="AB149" s="9"/>
+      <c r="AC149" s="9"/>
+      <c r="AD149" s="9"/>
+      <c r="AE149" s="9"/>
+      <c r="AF149" s="9"/>
+      <c r="AG149" s="9"/>
+      <c r="AH149" s="9"/>
+      <c r="AI149" s="9"/>
+      <c r="AJ149" s="9"/>
+      <c r="AK149" s="9"/>
+      <c r="AL149" s="9"/>
+      <c r="AM149" s="9"/>
+      <c r="AN149" s="9"/>
+      <c r="AO149" s="9"/>
+      <c r="AP149" s="9"/>
+      <c r="AQ149" s="9"/>
+      <c r="AR149" s="9"/>
+      <c r="AS149" s="9"/>
+      <c r="AT149" s="9"/>
+      <c r="AU149" s="9"/>
+      <c r="AV149" s="9"/>
+      <c r="AW149" s="44"/>
+      <c r="AX149" s="44"/>
+      <c r="AY149" s="44"/>
+      <c r="AZ149" s="44"/>
+      <c r="BA149" s="44"/>
+      <c r="BB149" s="44"/>
+      <c r="BC149" s="44"/>
+    </row>
+    <row r="150" spans="1:79" s="43" customFormat="1">
+      <c r="A150" s="9"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9"/>
+      <c r="D150" s="9"/>
+      <c r="E150" s="9"/>
+      <c r="F150" s="9"/>
+      <c r="G150" s="9"/>
+      <c r="H150" s="9"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="9"/>
+      <c r="K150" s="9"/>
+      <c r="L150" s="9"/>
+      <c r="M150" s="9"/>
+      <c r="N150" s="9"/>
+      <c r="O150" s="9"/>
+      <c r="P150" s="9"/>
+      <c r="Q150" s="9"/>
+      <c r="R150" s="9"/>
+      <c r="S150" s="9"/>
+      <c r="T150" s="9"/>
+      <c r="U150" s="9"/>
+      <c r="V150" s="9"/>
+      <c r="W150" s="9"/>
+      <c r="X150" s="9"/>
+      <c r="Y150" s="9"/>
+      <c r="Z150" s="9"/>
+      <c r="AA150" s="9"/>
+      <c r="AB150" s="9"/>
+      <c r="AC150" s="9"/>
+      <c r="AD150" s="9"/>
+      <c r="AE150" s="9"/>
+      <c r="AF150" s="9"/>
+      <c r="AG150" s="9"/>
+      <c r="AH150" s="9"/>
+      <c r="AI150" s="9"/>
+      <c r="AJ150" s="9"/>
+      <c r="AK150" s="9"/>
+      <c r="AL150" s="9"/>
+      <c r="AM150" s="9"/>
+      <c r="AN150" s="9"/>
+      <c r="AO150" s="9"/>
+      <c r="AP150" s="9"/>
+      <c r="AQ150" s="9"/>
+      <c r="AR150" s="9"/>
+      <c r="AS150" s="9"/>
+      <c r="AT150" s="9"/>
+      <c r="AU150" s="9"/>
+      <c r="AV150" s="9"/>
+      <c r="AW150" s="44"/>
+      <c r="AX150" s="44"/>
+      <c r="AY150" s="44"/>
+      <c r="AZ150" s="44"/>
+      <c r="BA150" s="44"/>
+      <c r="BB150" s="44"/>
+      <c r="BC150" s="44"/>
+    </row>
+    <row r="151" spans="1:79" s="43" customFormat="1" ht="15">
+      <c r="A151" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="9"/>
+      <c r="E151" s="9"/>
+      <c r="F151" s="9"/>
+      <c r="G151" s="9"/>
+      <c r="H151" s="9"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="9"/>
+      <c r="K151" s="9"/>
+      <c r="L151" s="9"/>
+      <c r="M151" s="9"/>
+      <c r="N151" s="9"/>
+      <c r="O151" s="9"/>
+      <c r="P151" s="9"/>
+      <c r="Q151" s="9"/>
+      <c r="R151" s="9"/>
+      <c r="S151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
+      <c r="V151" s="9"/>
+      <c r="W151" s="9"/>
+      <c r="X151" s="9"/>
+      <c r="Y151" s="9"/>
+      <c r="Z151" s="9"/>
+      <c r="AA151" s="9"/>
+      <c r="AB151" s="9"/>
+      <c r="AC151" s="9"/>
+      <c r="AD151" s="9"/>
+      <c r="AE151" s="9"/>
+      <c r="AF151" s="9"/>
+      <c r="AG151" s="9"/>
+      <c r="AH151" s="9"/>
+      <c r="AI151" s="9"/>
+      <c r="AJ151" s="9"/>
+      <c r="AK151" s="9"/>
+      <c r="AL151" s="9"/>
+      <c r="AM151" s="9"/>
+      <c r="AN151" s="9"/>
+      <c r="AO151" s="9"/>
+      <c r="AP151" s="9"/>
+      <c r="AQ151" s="9"/>
+      <c r="AR151" s="9"/>
+      <c r="AS151" s="9"/>
+      <c r="AT151" s="9"/>
+      <c r="AU151" s="9"/>
+      <c r="AV151" s="9"/>
+      <c r="AW151" s="44"/>
+      <c r="AX151" s="44"/>
+      <c r="AY151" s="44"/>
+      <c r="AZ151" s="44"/>
+      <c r="BA151" s="44"/>
+      <c r="BB151" s="44"/>
+      <c r="BC151" s="44"/>
+    </row>
+    <row r="152" spans="1:79" s="43" customFormat="1" ht="15">
+      <c r="A152" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="9"/>
+      <c r="E152" s="9"/>
+      <c r="F152" s="9"/>
+      <c r="G152" s="9"/>
+      <c r="H152" s="9"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="9"/>
+      <c r="K152" s="9"/>
+      <c r="L152" s="9"/>
+      <c r="M152" s="9"/>
+      <c r="N152" s="9"/>
+      <c r="O152" s="9"/>
+      <c r="P152" s="9"/>
+      <c r="Q152" s="9"/>
+      <c r="R152" s="9"/>
+      <c r="S152" s="9"/>
+      <c r="T152" s="9"/>
+      <c r="U152" s="9"/>
+      <c r="V152" s="9"/>
+      <c r="W152" s="9"/>
+      <c r="X152" s="9"/>
+      <c r="Y152" s="9"/>
+      <c r="Z152" s="9"/>
+      <c r="AA152" s="9"/>
+      <c r="AB152" s="9"/>
+      <c r="AC152" s="9"/>
+      <c r="AD152" s="9"/>
+      <c r="AE152" s="9"/>
+      <c r="AF152" s="9"/>
+      <c r="AG152" s="9"/>
+      <c r="AH152" s="9"/>
+      <c r="AI152" s="9"/>
+      <c r="AJ152" s="9"/>
+      <c r="AK152" s="9"/>
+      <c r="AL152" s="9"/>
+      <c r="AM152" s="9"/>
+      <c r="AN152" s="9"/>
+      <c r="AO152" s="9"/>
+      <c r="AP152" s="9"/>
+      <c r="AQ152" s="9"/>
+      <c r="AR152" s="9"/>
+      <c r="AS152" s="9"/>
+      <c r="AT152" s="9"/>
+      <c r="AU152" s="9"/>
+      <c r="AV152" s="9"/>
+      <c r="AW152" s="44"/>
+      <c r="AX152" s="44"/>
+      <c r="AY152" s="44"/>
+      <c r="AZ152" s="44"/>
+      <c r="BA152" s="44"/>
+      <c r="BB152" s="44"/>
+      <c r="BC152" s="44"/>
+    </row>
+    <row r="153" spans="1:79" s="43" customFormat="1" ht="15" thickBot="1">
+      <c r="A153" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
+      <c r="E153" s="9"/>
+      <c r="F153" s="9"/>
+      <c r="G153" s="9"/>
+      <c r="H153" s="9"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="9"/>
+      <c r="K153" s="9"/>
+      <c r="L153" s="9"/>
+      <c r="M153" s="9"/>
+      <c r="N153" s="9"/>
+      <c r="O153" s="9"/>
+      <c r="P153" s="9"/>
+      <c r="Q153" s="9"/>
+      <c r="R153" s="9"/>
+      <c r="S153" s="9"/>
+      <c r="T153" s="9"/>
+      <c r="U153" s="9"/>
+      <c r="V153" s="9"/>
+      <c r="W153" s="9"/>
+      <c r="X153" s="9"/>
+      <c r="Y153" s="9"/>
+      <c r="Z153" s="9"/>
+      <c r="AA153" s="9"/>
+      <c r="AB153" s="9"/>
+      <c r="AC153" s="9"/>
+      <c r="AD153" s="9"/>
+      <c r="AE153" s="9"/>
+      <c r="AF153" s="9"/>
+      <c r="AG153" s="9"/>
+      <c r="AH153" s="9"/>
+      <c r="AI153" s="9"/>
+      <c r="AJ153" s="9"/>
+      <c r="AK153" s="9"/>
+      <c r="AL153" s="9"/>
+      <c r="AM153" s="9"/>
+      <c r="AN153" s="9"/>
+      <c r="AO153" s="9"/>
+      <c r="AP153" s="9"/>
+      <c r="AQ153" s="9"/>
+      <c r="AR153" s="9"/>
+      <c r="AS153" s="9"/>
+      <c r="AT153" s="9"/>
+      <c r="AU153" s="9"/>
+      <c r="AV153" s="9"/>
+      <c r="AW153" s="44"/>
+      <c r="AX153" s="44"/>
+      <c r="AY153" s="44"/>
+      <c r="AZ153" s="44"/>
+      <c r="BA153" s="44"/>
+      <c r="BB153" s="44"/>
+      <c r="BC153" s="44"/>
+    </row>
+    <row r="154" spans="1:79" s="19" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A154" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="155" spans="1:79" ht="15">
+      <c r="A155" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB155" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AB121" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="BC121" s="13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="122" spans="1:55">
-      <c r="A122" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB122" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="BC122" s="14"/>
-    </row>
-    <row r="123" spans="1:55">
-      <c r="AB123" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC123" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="124" spans="1:55" ht="15">
-      <c r="A124" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB124" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="BC124" s="13" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="125" spans="1:55">
-      <c r="A125" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB125" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC125" s="13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="126" spans="1:55">
-      <c r="AB126" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="BC126" s="13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="127" spans="1:55">
-      <c r="AB127" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="BC127" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="128" spans="1:55">
-      <c r="AB128" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="BC128" s="13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="129" spans="28:55">
-      <c r="AB129" s="13" t="s">
+      <c r="BC155" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="BC129" s="13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="130" spans="28:55">
-      <c r="AB130" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BC130" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="131" spans="28:55">
-      <c r="BC131" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="132" spans="28:55" ht="15">
-      <c r="AB132" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BC132" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" spans="28:55">
-      <c r="AB133" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="BC133" s="13" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="134" spans="28:55">
-      <c r="BC134" s="13" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="135" spans="28:55">
-      <c r="BC135" s="13" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="136" spans="28:55">
-      <c r="BC136" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" spans="28:55">
-      <c r="BC137" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="138" spans="28:55">
-      <c r="BC138" s="14"/>
-    </row>
-    <row r="139" spans="28:55">
-      <c r="BC139" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="140" spans="28:55">
-      <c r="BC140" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="141" spans="28:55">
-      <c r="BC141" s="14"/>
-    </row>
-    <row r="142" spans="28:55">
-      <c r="BC142" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="28:55">
-      <c r="BC143" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="144" spans="28:55">
-      <c r="BC144" s="13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="145" spans="1:92">
-      <c r="BC145" s="13" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="146" spans="1:92">
-      <c r="BC146" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="147" spans="1:92">
-      <c r="BC147" s="13" t="s">
+      <c r="CA155" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="148" spans="1:92">
-      <c r="BC148" s="13" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="149" spans="1:92">
-      <c r="BC149" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="151" spans="1:92" ht="15">
-      <c r="BC151" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="152" spans="1:92" ht="15">
-      <c r="BC152" s="11" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="153" spans="1:92" ht="15" thickBot="1"/>
-    <row r="154" spans="1:92" s="19" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A154" s="18" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="155" spans="1:92" ht="15">
-      <c r="A155" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-      <c r="H155" s="16"/>
-      <c r="I155" s="16"/>
-      <c r="J155" s="16"/>
-      <c r="K155" s="16"/>
-      <c r="L155" s="16"/>
-      <c r="M155" s="16"/>
-      <c r="N155" s="16"/>
-      <c r="O155" s="16"/>
-      <c r="P155" s="16"/>
-      <c r="AG155" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="AH155" s="16"/>
-      <c r="AI155" s="16"/>
-      <c r="AJ155" s="16"/>
-      <c r="AK155" s="16"/>
-      <c r="AL155" s="16"/>
-      <c r="AM155" s="16"/>
-      <c r="AN155" s="16"/>
-      <c r="AO155" s="16"/>
-      <c r="AP155" s="16"/>
-      <c r="AQ155" s="16"/>
-      <c r="AR155" s="16"/>
-      <c r="AS155" s="16"/>
-      <c r="AT155" s="16"/>
-      <c r="AU155" s="16"/>
-      <c r="AV155" s="16"/>
-      <c r="AW155" s="16"/>
-      <c r="AX155" s="16"/>
-      <c r="BK155" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="BL155" s="16"/>
-      <c r="BM155" s="16"/>
-      <c r="BN155" s="16"/>
-      <c r="BO155" s="16"/>
-      <c r="BP155" s="16"/>
-      <c r="BQ155" s="16"/>
-      <c r="BR155" s="16"/>
-      <c r="BS155" s="16"/>
-      <c r="BT155" s="16"/>
-      <c r="BU155" s="16"/>
-      <c r="BV155" s="16"/>
-      <c r="BW155" s="16"/>
-      <c r="CN155" s="10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="156" spans="1:92" ht="15">
+    <row r="156" spans="1:79" ht="15">
       <c r="A156" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AG156" s="7" t="s">
+      <c r="AB156" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="BK156" s="7" t="s">
+      <c r="BC156" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="CN156" s="7" t="s">
+      <c r="CA156" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:92">
-      <c r="A157" s="21" t="s">
+    <row r="157" spans="1:79" ht="15">
+      <c r="A157" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB157" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="BC157" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="CA157" s="11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="158" spans="1:79" ht="15">
+      <c r="AB158" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="BC158" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="CA158" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="159" spans="1:79" ht="15">
+      <c r="A159" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="CA159" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="160" spans="1:79" ht="15">
+      <c r="A160" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB160" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="BC160" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="CA160" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="161" spans="1:79">
+      <c r="A161" s="14"/>
+      <c r="AB161" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="BC161" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="CA161" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="162" spans="1:79">
+      <c r="A162" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB162" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="BC162" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="CA162" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="163" spans="1:79">
+      <c r="A163" s="14"/>
+      <c r="BC163" s="14"/>
+    </row>
+    <row r="164" spans="1:79" ht="15">
+      <c r="A164" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB164" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="BC164" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="CA164" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="165" spans="1:79" ht="15">
+      <c r="A165" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB165" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="BC165" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="CA165" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="166" spans="1:79">
+      <c r="A166" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB166" s="14"/>
+      <c r="BC166" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="167" spans="1:79">
+      <c r="A167" s="14"/>
+      <c r="AB167" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="BC167" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="168" spans="1:79">
+      <c r="A168" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB168" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="BC168" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="169" spans="1:79">
+      <c r="A169" s="14"/>
+      <c r="AB169" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="BC169" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="170" spans="1:79">
+      <c r="A170" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB170" s="14"/>
+      <c r="BC170" s="14"/>
+    </row>
+    <row r="171" spans="1:79">
+      <c r="A171" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB171" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="BC171" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="172" spans="1:79">
+      <c r="A172" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB172" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="BC172" s="14"/>
+    </row>
+    <row r="173" spans="1:79">
+      <c r="A173" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB173" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="BC173" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="174" spans="1:79">
+      <c r="A174" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB174" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC174" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="175" spans="1:79">
+      <c r="A175" s="14"/>
+      <c r="AB175" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="BC175" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="176" spans="1:79">
+      <c r="A176" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB176" s="14"/>
+      <c r="BC176" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="177" spans="1:55">
+      <c r="A177" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB177" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="BC177" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="178" spans="1:55">
+      <c r="A178" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB178" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="BC178" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="179" spans="1:55">
+      <c r="A179" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB179" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="BC179" s="14"/>
+    </row>
+    <row r="180" spans="1:55">
+      <c r="AB180" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="BC180" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="181" spans="1:55" ht="15">
+      <c r="A181" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB181" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="BC181" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="182" spans="1:55">
+      <c r="A182" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB182" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC182" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="183" spans="1:55">
+      <c r="AB183" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC183" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="184" spans="1:55">
+      <c r="AB184" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="BC184" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="185" spans="1:55">
+      <c r="AB185" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="BC185" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="186" spans="1:55">
+      <c r="AB186" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="BC186" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="187" spans="1:55">
+      <c r="AB187" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC187" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="188" spans="1:55">
+      <c r="BC188" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="189" spans="1:55" ht="15">
+      <c r="AB189" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BC189" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="190" spans="1:55">
+      <c r="AB190" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="BC190" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="191" spans="1:55">
+      <c r="BC191" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="192" spans="1:55">
+      <c r="BC192" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="193" spans="55:55">
+      <c r="BC193" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="194" spans="55:55">
+      <c r="BC194" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="195" spans="55:55">
+      <c r="BC195" s="14"/>
+    </row>
+    <row r="196" spans="55:55">
+      <c r="BC196" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="197" spans="55:55">
+      <c r="BC197" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="198" spans="55:55">
+      <c r="BC198" s="14"/>
+    </row>
+    <row r="199" spans="55:55">
+      <c r="BC199" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="200" spans="55:55">
+      <c r="BC200" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="201" spans="55:55">
+      <c r="BC201" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="202" spans="55:55">
+      <c r="BC202" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="203" spans="55:55">
+      <c r="BC203" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="204" spans="55:55">
+      <c r="BC204" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="205" spans="55:55">
+      <c r="BC205" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="206" spans="55:55">
+      <c r="BC206" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="208" spans="55:55" ht="15">
+      <c r="BC208" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="209" spans="1:92" ht="15">
+      <c r="BC209" s="11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="210" spans="1:92" ht="15" thickBot="1"/>
+    <row r="211" spans="1:92" s="19" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A211" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="212" spans="1:92" ht="15">
+      <c r="A212" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B212" s="16"/>
+      <c r="C212" s="16"/>
+      <c r="D212" s="16"/>
+      <c r="E212" s="16"/>
+      <c r="F212" s="16"/>
+      <c r="G212" s="16"/>
+      <c r="H212" s="16"/>
+      <c r="I212" s="16"/>
+      <c r="J212" s="16"/>
+      <c r="K212" s="16"/>
+      <c r="L212" s="16"/>
+      <c r="M212" s="16"/>
+      <c r="N212" s="16"/>
+      <c r="O212" s="16"/>
+      <c r="P212" s="16"/>
+      <c r="AG212" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="AH212" s="16"/>
+      <c r="AI212" s="16"/>
+      <c r="AJ212" s="16"/>
+      <c r="AK212" s="16"/>
+      <c r="AL212" s="16"/>
+      <c r="AM212" s="16"/>
+      <c r="AN212" s="16"/>
+      <c r="AO212" s="16"/>
+      <c r="AP212" s="16"/>
+      <c r="AQ212" s="16"/>
+      <c r="AR212" s="16"/>
+      <c r="AS212" s="16"/>
+      <c r="AT212" s="16"/>
+      <c r="AU212" s="16"/>
+      <c r="AV212" s="16"/>
+      <c r="AW212" s="16"/>
+      <c r="AX212" s="16"/>
+      <c r="BK212" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="BL212" s="16"/>
+      <c r="BM212" s="16"/>
+      <c r="BN212" s="16"/>
+      <c r="BO212" s="16"/>
+      <c r="BP212" s="16"/>
+      <c r="BQ212" s="16"/>
+      <c r="BR212" s="16"/>
+      <c r="BS212" s="16"/>
+      <c r="BT212" s="16"/>
+      <c r="BU212" s="16"/>
+      <c r="BV212" s="16"/>
+      <c r="BW212" s="16"/>
+      <c r="CN212" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="213" spans="1:92" ht="15">
+      <c r="A213" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG213" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="BK213" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="CN213" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="214" spans="1:92">
+      <c r="A214" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG214" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="BK214" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="CN214" s="11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="215" spans="1:92" ht="15">
+      <c r="A215" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="BK215" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="CN215" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="216" spans="1:92" ht="15">
+      <c r="AG216" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="217" spans="1:92" ht="15">
+      <c r="A217" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG217" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="BK217" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="CN217" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="218" spans="1:92">
+      <c r="A218" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG218" s="14"/>
+      <c r="BK218" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="CN218" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="219" spans="1:92">
+      <c r="A219" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG219" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="AH219" s="20"/>
+      <c r="AI219" s="20"/>
+      <c r="AJ219" s="20"/>
+      <c r="AK219" s="20"/>
+      <c r="AL219" s="20"/>
+      <c r="AM219" s="20"/>
+      <c r="AN219" s="20"/>
+      <c r="AO219" s="20"/>
+      <c r="AP219" s="20"/>
+      <c r="AQ219" s="20"/>
+      <c r="AR219" s="20"/>
+      <c r="AS219" s="20"/>
+      <c r="AT219" s="20"/>
+      <c r="BK219" s="14"/>
+      <c r="CN219" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="220" spans="1:92">
+      <c r="A220" s="14"/>
+      <c r="AG220" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="BK220" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="CN220" s="14"/>
+    </row>
+    <row r="221" spans="1:92">
+      <c r="A221" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="AG157" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="BK157" s="21" t="s">
+      <c r="AG221" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="BK221" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="CN157" s="11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="158" spans="1:92" ht="15">
-      <c r="A158" s="21" t="s">
+      <c r="CN221" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="222" spans="1:92">
+      <c r="A222" s="14"/>
+      <c r="AG222" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="BK222" s="14"/>
+      <c r="CN222" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="223" spans="1:92">
+      <c r="A223" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="BK158" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="CN158" s="11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="159" spans="1:92" ht="15">
-      <c r="AG159" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="160" spans="1:92" ht="15">
-      <c r="A160" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="AG160" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="BK160" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="CN160" s="7" t="s">
+      <c r="AG223" s="14"/>
+      <c r="BK223" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="CN223" s="14"/>
+    </row>
+    <row r="224" spans="1:92" ht="15">
+      <c r="A224" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="AG224" s="17" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="161" spans="1:92">
-      <c r="A161" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG161" s="14"/>
-      <c r="BK161" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="CN161" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="162" spans="1:92">
-      <c r="A162" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG162" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="AH162" s="20"/>
-      <c r="AI162" s="20"/>
-      <c r="AJ162" s="20"/>
-      <c r="AK162" s="20"/>
-      <c r="AL162" s="20"/>
-      <c r="AM162" s="20"/>
-      <c r="AN162" s="20"/>
-      <c r="AO162" s="20"/>
-      <c r="AP162" s="20"/>
-      <c r="AQ162" s="20"/>
-      <c r="AR162" s="20"/>
-      <c r="AS162" s="20"/>
-      <c r="AT162" s="20"/>
-      <c r="BK162" s="14"/>
-      <c r="CN162" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="163" spans="1:92">
-      <c r="A163" s="14"/>
-      <c r="AG163" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="BK163" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="CN163" s="14"/>
-    </row>
-    <row r="164" spans="1:92">
-      <c r="A164" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="AG164" s="13" t="s">
+      <c r="BK224" s="14"/>
+      <c r="CN224" s="13" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="225" spans="1:92">
+      <c r="A225" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG225" s="14"/>
+      <c r="BK225" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="CN225" s="14"/>
+    </row>
+    <row r="226" spans="1:92">
+      <c r="A226" s="14"/>
+      <c r="AG226" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH226" s="20"/>
+      <c r="AI226" s="20"/>
+      <c r="AJ226" s="20"/>
+      <c r="AK226" s="20"/>
+      <c r="AL226" s="20"/>
+      <c r="AM226" s="20"/>
+      <c r="AN226" s="20"/>
+      <c r="AO226" s="20"/>
+      <c r="AP226" s="20"/>
+      <c r="AQ226" s="20"/>
+      <c r="AR226" s="20"/>
+      <c r="BK226" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="CN226" s="13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="227" spans="1:92">
+      <c r="A227" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AG227" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="BK164" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="CN164" s="13" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="165" spans="1:92">
-      <c r="A165" s="14"/>
-      <c r="AG165" s="13" t="s">
+      <c r="AH227" s="20"/>
+      <c r="AI227" s="20"/>
+      <c r="AJ227" s="20"/>
+      <c r="AK227" s="20"/>
+      <c r="AL227" s="20"/>
+      <c r="AM227" s="20"/>
+      <c r="AN227" s="20"/>
+      <c r="AO227" s="20"/>
+      <c r="AP227" s="20"/>
+      <c r="AQ227" s="20"/>
+      <c r="AR227" s="20"/>
+      <c r="BK227" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="CN227" s="13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="228" spans="1:92">
+      <c r="A228" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="AG228" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="BK165" s="14"/>
-      <c r="CN165" s="13" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="166" spans="1:92">
-      <c r="A166" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="AG166" s="14"/>
-      <c r="BK166" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="CN166" s="14"/>
-    </row>
-    <row r="167" spans="1:92" ht="15">
-      <c r="A167" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AG167" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="BK167" s="14"/>
-      <c r="CN167" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="168" spans="1:92">
-      <c r="A168" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="AG168" s="14"/>
-      <c r="BK168" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="CN168" s="14"/>
-    </row>
-    <row r="169" spans="1:92">
-      <c r="A169" s="14"/>
-      <c r="AG169" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH169" s="20"/>
-      <c r="AI169" s="20"/>
-      <c r="AJ169" s="20"/>
-      <c r="AK169" s="20"/>
-      <c r="AL169" s="20"/>
-      <c r="AM169" s="20"/>
-      <c r="AN169" s="20"/>
-      <c r="AO169" s="20"/>
-      <c r="AP169" s="20"/>
-      <c r="AQ169" s="20"/>
-      <c r="AR169" s="20"/>
-      <c r="BK169" s="13" t="s">
+      <c r="AH228" s="20"/>
+      <c r="AI228" s="20"/>
+      <c r="AJ228" s="20"/>
+      <c r="AK228" s="20"/>
+      <c r="AL228" s="20"/>
+      <c r="AM228" s="20"/>
+      <c r="AN228" s="20"/>
+      <c r="AO228" s="20"/>
+      <c r="AP228" s="20"/>
+      <c r="AQ228" s="20"/>
+      <c r="AR228" s="20"/>
+      <c r="BK228" s="14"/>
+      <c r="CN228" s="13" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="229" spans="1:92">
+      <c r="A229" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="AG229" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH229" s="20"/>
+      <c r="AI229" s="20"/>
+      <c r="AJ229" s="20"/>
+      <c r="AK229" s="20"/>
+      <c r="AL229" s="20"/>
+      <c r="AM229" s="20"/>
+      <c r="AN229" s="20"/>
+      <c r="AO229" s="20"/>
+      <c r="AP229" s="20"/>
+      <c r="AQ229" s="20"/>
+      <c r="AR229" s="20"/>
+      <c r="BK229" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="CN169" s="13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="170" spans="1:92">
-      <c r="A170" s="13" t="s">
+      <c r="CN229" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="230" spans="1:92">
+      <c r="A230" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="BK230" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="CN230" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="231" spans="1:92" ht="15">
+      <c r="A231" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="AG231" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK231" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="CN231" s="13" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="232" spans="1:92">
+      <c r="A232" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="AG232" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="BK232" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="CN232" s="13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="233" spans="1:92">
+      <c r="A233" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK233" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="CN233" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="234" spans="1:92">
+      <c r="A234" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK234" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="CN234" s="14"/>
+    </row>
+    <row r="235" spans="1:92">
+      <c r="A235" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="BK235" s="14"/>
+      <c r="CN235" s="13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="236" spans="1:92">
+      <c r="A236" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="AG170" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="AH170" s="20"/>
-      <c r="AI170" s="20"/>
-      <c r="AJ170" s="20"/>
-      <c r="AK170" s="20"/>
-      <c r="AL170" s="20"/>
-      <c r="AM170" s="20"/>
-      <c r="AN170" s="20"/>
-      <c r="AO170" s="20"/>
-      <c r="AP170" s="20"/>
-      <c r="AQ170" s="20"/>
-      <c r="AR170" s="20"/>
-      <c r="BK170" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="CN170" s="13" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="171" spans="1:92">
-      <c r="A171" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="AG171" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="AH171" s="20"/>
-      <c r="AI171" s="20"/>
-      <c r="AJ171" s="20"/>
-      <c r="AK171" s="20"/>
-      <c r="AL171" s="20"/>
-      <c r="AM171" s="20"/>
-      <c r="AN171" s="20"/>
-      <c r="AO171" s="20"/>
-      <c r="AP171" s="20"/>
-      <c r="AQ171" s="20"/>
-      <c r="AR171" s="20"/>
-      <c r="BK171" s="14"/>
-      <c r="CN171" s="13" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="172" spans="1:92">
-      <c r="A172" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="AG172" s="17" t="s">
+      <c r="BK236" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="CN236" s="13" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="237" spans="1:92">
+      <c r="A237" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="BK237" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="CN237" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="238" spans="1:92">
+      <c r="A238" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="BK238" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="CN238" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="239" spans="1:92">
+      <c r="A239" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AH172" s="20"/>
-      <c r="AI172" s="20"/>
-      <c r="AJ172" s="20"/>
-      <c r="AK172" s="20"/>
-      <c r="AL172" s="20"/>
-      <c r="AM172" s="20"/>
-      <c r="AN172" s="20"/>
-      <c r="AO172" s="20"/>
-      <c r="AP172" s="20"/>
-      <c r="AQ172" s="20"/>
-      <c r="AR172" s="20"/>
-      <c r="BK172" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="CN172" s="13" t="s">
+      <c r="BK239" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="CN239" s="13" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="240" spans="1:92">
+      <c r="A240" s="14"/>
+      <c r="BK240" s="13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="173" spans="1:92">
-      <c r="A173" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="BK173" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="CN173" s="13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="174" spans="1:92" ht="15">
-      <c r="A174" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="AG174" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BK174" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="CN174" s="13" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="175" spans="1:92">
-      <c r="A175" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="AG175" s="11" t="s">
+      <c r="CN240" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="241" spans="1:92">
+      <c r="A241" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="BK241" s="14"/>
+      <c r="CN241" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="242" spans="1:92">
+      <c r="A242" s="14"/>
+      <c r="BK242" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="CN242" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="243" spans="1:92">
+      <c r="A243" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="BK243" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="CN243" s="14"/>
+    </row>
+    <row r="244" spans="1:92">
+      <c r="A244" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="BK244" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="CN244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="1:92">
+      <c r="A245" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="BK245" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="CN245" s="13" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="246" spans="1:92">
+      <c r="A246" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="BK246" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="CN246" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="247" spans="1:92">
+      <c r="A247" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK247" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="CN247" s="13" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="248" spans="1:92">
+      <c r="CN248" s="13" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="249" spans="1:92" ht="15">
+      <c r="A249" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BK249" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="CN249" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="250" spans="1:92" ht="15">
+      <c r="A250" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="BK250" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="BK175" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="CN175" s="13" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="176" spans="1:92">
-      <c r="A176" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK176" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="CN176" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="177" spans="1:92">
-      <c r="A177" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK177" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="CN177" s="14"/>
-    </row>
-    <row r="178" spans="1:92">
-      <c r="A178" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="BK178" s="14"/>
-      <c r="CN178" s="13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="179" spans="1:92">
-      <c r="A179" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="BK179" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="CN179" s="13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="180" spans="1:92">
-      <c r="A180" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="BK180" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="CN180" s="13" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="181" spans="1:92">
-      <c r="A181" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="BK181" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="CN181" s="13" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="182" spans="1:92">
-      <c r="A182" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK182" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="CN182" s="13" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="183" spans="1:92">
-      <c r="A183" s="14"/>
-      <c r="BK183" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="CN183" s="13" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="184" spans="1:92">
-      <c r="A184" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="BK184" s="14"/>
-      <c r="CN184" s="13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="185" spans="1:92">
-      <c r="A185" s="14"/>
-      <c r="BK185" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="CN185" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="186" spans="1:92">
-      <c r="A186" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK186" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="CN186" s="14"/>
-    </row>
-    <row r="187" spans="1:92">
-      <c r="A187" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="BK187" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="CN187" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="188" spans="1:92">
-      <c r="A188" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="BK188" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="CN188" s="13" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="189" spans="1:92">
-      <c r="A189" s="13" t="s">
+    </row>
+    <row r="251" spans="1:92" ht="15">
+      <c r="A251" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="BK189" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="CN189" s="13" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="190" spans="1:92">
-      <c r="A190" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="BK190" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="CN190" s="13" t="s">
+      <c r="CN251" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="252" spans="1:92">
+      <c r="CN252" s="11" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="191" spans="1:92">
-      <c r="CN191" s="13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="192" spans="1:92" ht="15">
-      <c r="A192" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BK192" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="CN192" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="193" spans="1:92" ht="15">
-      <c r="A193" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="BK193" s="11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="194" spans="1:92" ht="15">
-      <c r="A194" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="CN194" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="195" spans="1:92">
-      <c r="CN195" s="11" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="198" spans="1:92">
-      <c r="A198" s="11"/>
-    </row>
-    <row r="199" spans="1:92">
-      <c r="A199" s="11"/>
-    </row>
-    <row r="200" spans="1:92">
-      <c r="A200" s="11"/>
-    </row>
-    <row r="201" spans="1:92">
-      <c r="A201" s="11"/>
-    </row>
-    <row r="202" spans="1:92">
-      <c r="A202" s="11"/>
-    </row>
-    <row r="203" spans="1:92">
-      <c r="A203" s="11"/>
+    <row r="255" spans="1:92">
+      <c r="A255" s="11"/>
+    </row>
+    <row r="256" spans="1:92">
+      <c r="A256" s="11"/>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="11"/>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="11"/>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="11"/>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6175,92 +9798,92 @@
     </row>
     <row r="2" spans="1:23" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A2" s="18" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15">
       <c r="A3" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="15">
       <c r="A4" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="W4" s="11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15">
       <c r="A5" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="W5" s="11" t="s">
         <v>430</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15">
       <c r="A7" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="B8" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="B9" s="13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="B10" s="13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15">
       <c r="B11" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15">
       <c r="B12" s="13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="B13" s="14"/>
       <c r="W13" s="11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="B14" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="B15" s="13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -6275,7 +9898,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="B18" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6283,22 +9906,22 @@
     </row>
     <row r="20" spans="1:2">
       <c r="B20" s="13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" s="13" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="B22" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="B23" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6308,38 +9931,38 @@
     </row>
     <row r="25" spans="1:2">
       <c r="B25" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="B26" s="13" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15">
       <c r="A28" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="11" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15" thickBot="1"/>
     <row r="33" spans="1:43" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A33" s="18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" spans="1:43" ht="15">
       <c r="A34" s="15" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -6348,7 +9971,7 @@
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
       <c r="Y34" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Z34" s="16"/>
       <c r="AA34" s="16"/>
@@ -6360,12 +9983,12 @@
       <c r="AG34" s="16"/>
       <c r="AH34" s="16"/>
       <c r="AQ34" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:43" ht="15">
       <c r="A35" s="11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="O35" s="27"/>
       <c r="P35" s="27"/>
@@ -6373,10 +9996,10 @@
       <c r="R35" s="27"/>
       <c r="S35" s="27"/>
       <c r="Y35" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AQ35" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:43">
@@ -6388,15 +10011,15 @@
       <c r="U36" s="27"/>
       <c r="V36" s="27"/>
       <c r="Y36" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AQ36" s="11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="37" spans="1:43" ht="15">
       <c r="A37" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="R37" s="27"/>
       <c r="T37" s="27"/>
@@ -6427,15 +10050,15 @@
       <c r="U38" s="27"/>
       <c r="V38" s="27"/>
       <c r="Y38" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AQ38" s="10" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:43" ht="15">
       <c r="B39" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C39" s="29"/>
       <c r="D39" s="29"/>
@@ -6456,15 +10079,15 @@
       <c r="U39" s="27"/>
       <c r="V39" s="27"/>
       <c r="Z39" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AQ39" s="11" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:43" ht="15">
       <c r="B40" s="28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C40" s="29"/>
       <c r="D40" s="29"/>
@@ -6487,10 +10110,10 @@
       <c r="U40" s="27"/>
       <c r="V40" s="27"/>
       <c r="Z40" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AQ40" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="1:43" ht="15">
@@ -6516,7 +10139,7 @@
       <c r="U41" s="27"/>
       <c r="V41" s="27"/>
       <c r="Z41" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:43" ht="15">
@@ -6544,15 +10167,15 @@
       <c r="U42" s="27"/>
       <c r="V42" s="27"/>
       <c r="Z42" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AQ42" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" spans="1:43" ht="15">
       <c r="B43" s="28" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
@@ -6576,12 +10199,12 @@
       <c r="V43" s="27"/>
       <c r="Z43" s="14"/>
       <c r="AQ43" s="13" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="44" spans="1:43" ht="15">
       <c r="B44" s="28" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
@@ -6599,12 +10222,12 @@
       <c r="P44" s="29"/>
       <c r="Q44" s="29"/>
       <c r="Z44" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" spans="1:43" ht="15">
       <c r="B45" s="28" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C45" s="29"/>
       <c r="D45" s="29"/>
@@ -6641,12 +10264,12 @@
       <c r="P46" s="29"/>
       <c r="Q46" s="29"/>
       <c r="Z46" s="13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47" spans="1:43" ht="15">
       <c r="B47" s="28" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C47" s="29"/>
       <c r="D47" s="29"/>
@@ -6664,7 +10287,7 @@
       <c r="P47" s="29"/>
       <c r="Q47" s="29"/>
       <c r="Z47" s="13" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:43" ht="15">
@@ -6685,12 +10308,12 @@
       <c r="P48" s="29"/>
       <c r="Q48" s="29"/>
       <c r="Z48" s="13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="49" spans="1:58" ht="15">
       <c r="B49" s="29" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
@@ -6711,23 +10334,23 @@
     </row>
     <row r="50" spans="1:58">
       <c r="Z50" s="13" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" spans="1:58">
       <c r="Z51" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="52" spans="1:58" ht="15" thickBot="1"/>
     <row r="53" spans="1:58" s="26" customFormat="1" ht="15.75" thickBot="1">
       <c r="A53" s="25" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" spans="1:58" ht="15">
       <c r="A54" s="15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -6738,7 +10361,7 @@
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
       <c r="S54" s="15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="T54" s="16"/>
       <c r="U54" s="16"/>
@@ -6748,7 +10371,7 @@
       <c r="Y54" s="16"/>
       <c r="Z54" s="16"/>
       <c r="AK54" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AL54" s="16"/>
       <c r="AM54" s="16"/>
@@ -6762,7 +10385,7 @@
       <c r="AU54" s="16"/>
       <c r="AV54" s="16"/>
       <c r="AX54" s="15" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AY54" s="16"/>
       <c r="AZ54" s="16"/>
@@ -6775,37 +10398,37 @@
     </row>
     <row r="55" spans="1:58" ht="15">
       <c r="A55" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="S55" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AK55" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="AL55" s="20"/>
       <c r="AX55" s="21" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AY55" s="20"/>
     </row>
     <row r="56" spans="1:58">
       <c r="A56" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AK56" s="21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AL56" s="20"/>
       <c r="AX56" s="21" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AY56" s="20"/>
     </row>
     <row r="57" spans="1:58" ht="15">
       <c r="R57" s="20"/>
       <c r="S57" s="29" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T57" s="20"/>
       <c r="U57" s="20"/>
@@ -6825,12 +10448,12 @@
     </row>
     <row r="58" spans="1:58" ht="15">
       <c r="A58" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="R58" s="20"/>
       <c r="S58" s="20"/>
       <c r="T58" s="17" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="U58" s="20"/>
       <c r="V58" s="20"/>
@@ -6847,17 +10470,17 @@
       <c r="AG58" s="20"/>
       <c r="AH58" s="20"/>
       <c r="AK58" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59" spans="1:58">
       <c r="A59" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R59" s="20"/>
       <c r="S59" s="20"/>
       <c r="T59" s="17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="U59" s="20"/>
       <c r="V59" s="20"/>
@@ -6874,14 +10497,14 @@
       <c r="AG59" s="20"/>
       <c r="AH59" s="20"/>
       <c r="AL59" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="60" spans="1:58">
       <c r="R60" s="20"/>
       <c r="S60" s="20"/>
       <c r="T60" s="17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="U60" s="20"/>
       <c r="V60" s="20"/>
@@ -6898,14 +10521,14 @@
       <c r="AG60" s="20"/>
       <c r="AH60" s="20"/>
       <c r="AL60" s="13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:58">
       <c r="R61" s="20"/>
       <c r="S61" s="20"/>
       <c r="T61" s="17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="U61" s="20"/>
       <c r="V61" s="20"/>
@@ -6922,14 +10545,14 @@
       <c r="AG61" s="20"/>
       <c r="AH61" s="20"/>
       <c r="AL61" s="13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" spans="1:58">
       <c r="R62" s="20"/>
       <c r="S62" s="20"/>
       <c r="T62" s="17" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="U62" s="20"/>
       <c r="V62" s="20"/>
@@ -6950,7 +10573,7 @@
       <c r="R63" s="20"/>
       <c r="S63" s="20"/>
       <c r="T63" s="17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="U63" s="20"/>
       <c r="V63" s="20"/>
@@ -7000,17 +10623,17 @@
   <sheetData>
     <row r="1" spans="1:53" s="9" customFormat="1" ht="15.75" thickBot="1">
       <c r="A1" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:53" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A2" s="18" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:53" s="9" customFormat="1" ht="15">
       <c r="A3" s="15" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -7031,7 +10654,7 @@
       <c r="R3" s="16"/>
       <c r="S3" s="16"/>
       <c r="V3" s="15" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="W3" s="16"/>
       <c r="X3" s="16"/>
@@ -7048,7 +10671,7 @@
       <c r="AI3" s="16"/>
       <c r="AJ3" s="16"/>
       <c r="AM3" s="15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AN3" s="16"/>
       <c r="AO3" s="16"/>
@@ -7067,114 +10690,114 @@
     </row>
     <row r="4" spans="1:53" s="9" customFormat="1" ht="15">
       <c r="A4" s="8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:53" s="9" customFormat="1">
       <c r="A5" s="22" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:53" s="9" customFormat="1">
       <c r="A6" s="22" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="V6" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:53" s="9" customFormat="1" ht="15">
       <c r="A7" s="22" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="V7" s="23" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AM7" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:53" s="9" customFormat="1">
       <c r="A8" s="11"/>
       <c r="V8" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AN8" s="13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:53" s="9" customFormat="1" ht="15">
       <c r="A9" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AN9" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:53" s="9" customFormat="1" ht="15">
       <c r="B10" s="13" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:53" s="9" customFormat="1">
       <c r="B11" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:53" s="9" customFormat="1">
       <c r="B12" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="W12" s="13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:53" s="9" customFormat="1">
       <c r="B13" s="14"/>
       <c r="W13" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:53" s="9" customFormat="1">
       <c r="B14" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="W14" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:53" s="9" customFormat="1">
       <c r="B15" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="W15" s="13" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:53" s="9" customFormat="1">
       <c r="B16" s="13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="W16" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:63" s="9" customFormat="1">
@@ -7182,58 +10805,58 @@
     </row>
     <row r="18" spans="1:63" s="9" customFormat="1" ht="15">
       <c r="A18" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="W18" s="13" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:63" s="9" customFormat="1">
       <c r="A19" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:63" s="9" customFormat="1" ht="15" thickBot="1"/>
     <row r="21" spans="1:63" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A21" s="18" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="1:63" s="9" customFormat="1" ht="15">
       <c r="A22" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:63" s="9" customFormat="1">
       <c r="A23" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:63" s="9" customFormat="1"/>
     <row r="25" spans="1:63" s="9" customFormat="1" ht="15">
       <c r="A25" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:63" s="9" customFormat="1">
       <c r="B26" s="13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" spans="1:63" s="9" customFormat="1">
       <c r="B27" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:63" s="9" customFormat="1" ht="15" thickBot="1"/>
     <row r="29" spans="1:63" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A29" s="18" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" spans="1:63" s="9" customFormat="1" ht="15">
       <c r="A30" s="15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7247,14 +10870,14 @@
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="S30" s="15" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="T30" s="16"/>
       <c r="U30" s="16"/>
       <c r="V30" s="16"/>
       <c r="W30" s="16"/>
       <c r="AG30" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="AH30" s="16"/>
       <c r="AI30" s="16"/>
@@ -7270,7 +10893,7 @@
       <c r="AS30" s="16"/>
       <c r="AT30" s="16"/>
       <c r="BA30" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="BB30" s="16"/>
       <c r="BC30" s="16"/>
@@ -7285,39 +10908,39 @@
     </row>
     <row r="31" spans="1:63" s="9" customFormat="1">
       <c r="A31" s="21" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="S31" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="AG31" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="AG31" s="11" t="s">
-        <v>512</v>
-      </c>
       <c r="BA31" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="32" spans="1:63" s="9" customFormat="1" ht="15">
       <c r="A32" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
       <c r="S32" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="AG32" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="BA32" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" spans="1:54" s="9" customFormat="1">
       <c r="A33" s="31" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -7327,66 +10950,66 @@
     </row>
     <row r="34" spans="1:54" s="9" customFormat="1" ht="15">
       <c r="A34" s="32" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
       <c r="S34" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AH34" s="13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="BA34" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" spans="1:54" s="9" customFormat="1">
       <c r="T35" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AH35" s="13" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="BB35" s="13" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="36" spans="1:54" s="9" customFormat="1" ht="15">
       <c r="A36" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="T36" s="13" t="s">
         <v>52</v>
       </c>
       <c r="AH36" s="13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="BB36" s="13" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:54" s="9" customFormat="1">
       <c r="B37" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="T37" s="13" t="s">
         <v>50</v>
       </c>
       <c r="AH37" s="13" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="BB37" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" spans="1:54" s="9" customFormat="1">
       <c r="B38" s="17" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C38" s="20"/>
       <c r="T38" s="13" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AH38" s="14"/>
       <c r="BB38" s="13" t="s">
@@ -7395,41 +11018,41 @@
     </row>
     <row r="39" spans="1:54" s="9" customFormat="1">
       <c r="B39" s="17" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C39" s="20"/>
       <c r="T39" s="14"/>
       <c r="AH39" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="BB39" s="14"/>
     </row>
     <row r="40" spans="1:54" s="9" customFormat="1">
       <c r="B40" s="13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="T40" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AH40" s="13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="BB40" s="13" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="41" spans="1:54" s="9" customFormat="1">
       <c r="B41" s="13" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="T41" s="13" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AH41" s="13" t="s">
         <v>70</v>
       </c>
       <c r="BB41" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="42" spans="1:54" s="9" customFormat="1">
@@ -7437,10 +11060,10 @@
         <v>108</v>
       </c>
       <c r="T42" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="BB42" s="13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" spans="1:54" s="9" customFormat="1">
@@ -7451,7 +11074,7 @@
         <v>101</v>
       </c>
       <c r="BB43" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="44" spans="1:54" s="9" customFormat="1">
@@ -7465,47 +11088,47 @@
     <row r="45" spans="1:54" s="9" customFormat="1"/>
     <row r="46" spans="1:54" s="9" customFormat="1" ht="15">
       <c r="BA46" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="47" spans="1:54" s="9" customFormat="1" ht="15" thickBot="1">
       <c r="BA47" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="48" spans="1:54" s="19" customFormat="1" ht="15.75" thickBot="1">
       <c r="A48" s="18" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A49" s="8" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="50" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A50" s="8" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="51" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A51" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="52" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A52" s="8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A53" s="8" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="54" spans="1:1" s="9" customFormat="1" ht="15">
       <c r="A54" s="8" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="55" spans="1:1" s="9" customFormat="1"/>
